--- a/2026 pasta satış.xlsx
+++ b/2026 pasta satış.xlsx
@@ -400,10 +400,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1087,11 +1087,11 @@
       <c r="AG3" s="8">
         <v>116</v>
       </c>
-      <c r="AH3" s="18" t="s">
+      <c r="AH3" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AI3" s="18"/>
-      <c r="AJ3" s="18"/>
+      <c r="AI3" s="19"/>
+      <c r="AJ3" s="19"/>
       <c r="AK3" s="8">
         <v>0</v>
       </c>
@@ -1271,7 +1271,9 @@
       <c r="AU4" s="8">
         <v>115</v>
       </c>
-      <c r="AV4" s="8"/>
+      <c r="AV4" s="8">
+        <v>134</v>
+      </c>
     </row>
     <row r="5" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -1415,7 +1417,9 @@
       <c r="AU5" s="8">
         <v>69</v>
       </c>
-      <c r="AV5" s="8"/>
+      <c r="AV5" s="8">
+        <v>78</v>
+      </c>
     </row>
     <row r="6" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -1559,7 +1563,9 @@
       <c r="AU6" s="8">
         <v>59</v>
       </c>
-      <c r="AV6" s="8"/>
+      <c r="AV6" s="8">
+        <v>61</v>
+      </c>
     </row>
     <row r="7" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -1703,7 +1709,9 @@
       <c r="AU7" s="8">
         <v>142</v>
       </c>
-      <c r="AV7" s="8"/>
+      <c r="AV7" s="8">
+        <v>125</v>
+      </c>
     </row>
     <row r="8" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
@@ -1847,7 +1855,9 @@
       <c r="AU8" s="8">
         <v>144</v>
       </c>
-      <c r="AV8" s="8"/>
+      <c r="AV8" s="8">
+        <v>125</v>
+      </c>
     </row>
     <row r="9" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
@@ -1991,7 +2001,9 @@
       <c r="AU9" s="8">
         <v>126</v>
       </c>
-      <c r="AV9" s="8"/>
+      <c r="AV9" s="8">
+        <v>92</v>
+      </c>
     </row>
     <row r="10" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
@@ -2135,7 +2147,9 @@
       <c r="AU10" s="8">
         <v>124</v>
       </c>
-      <c r="AV10" s="8"/>
+      <c r="AV10" s="8">
+        <v>110</v>
+      </c>
     </row>
     <row r="11" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
@@ -2279,7 +2293,9 @@
       <c r="AU11" s="8">
         <v>73</v>
       </c>
-      <c r="AV11" s="8"/>
+      <c r="AV11" s="8">
+        <v>67</v>
+      </c>
     </row>
     <row r="12" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
@@ -2423,7 +2439,9 @@
       <c r="AU12" s="8">
         <v>71</v>
       </c>
-      <c r="AV12" s="8"/>
+      <c r="AV12" s="8">
+        <v>64</v>
+      </c>
     </row>
     <row r="13" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
@@ -2567,7 +2585,9 @@
       <c r="AU13" s="8">
         <v>133</v>
       </c>
-      <c r="AV13" s="8"/>
+      <c r="AV13" s="8">
+        <v>137</v>
+      </c>
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
@@ -2711,7 +2731,9 @@
       <c r="AU14" s="8">
         <v>129</v>
       </c>
-      <c r="AV14" s="8"/>
+      <c r="AV14" s="8">
+        <v>122</v>
+      </c>
     </row>
     <row r="15" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
@@ -2855,7 +2877,9 @@
       <c r="AU15" s="8">
         <v>146</v>
       </c>
-      <c r="AV15" s="8"/>
+      <c r="AV15" s="8">
+        <v>125</v>
+      </c>
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
@@ -2999,7 +3023,9 @@
       <c r="AU16" s="8">
         <v>114</v>
       </c>
-      <c r="AV16" s="8"/>
+      <c r="AV16" s="8">
+        <v>86</v>
+      </c>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
@@ -3143,7 +3169,9 @@
       <c r="AU17" s="8">
         <v>89</v>
       </c>
-      <c r="AV17" s="8"/>
+      <c r="AV17" s="8">
+        <v>84</v>
+      </c>
     </row>
     <row r="18" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
@@ -3287,7 +3315,9 @@
       <c r="AU18" s="8">
         <v>55</v>
       </c>
-      <c r="AV18" s="8"/>
+      <c r="AV18" s="8">
+        <v>43</v>
+      </c>
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
@@ -3431,7 +3461,9 @@
       <c r="AU19" s="8">
         <v>48</v>
       </c>
-      <c r="AV19" s="8"/>
+      <c r="AV19" s="8">
+        <v>49</v>
+      </c>
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
@@ -3575,7 +3607,9 @@
       <c r="AU20" s="8">
         <v>121</v>
       </c>
-      <c r="AV20" s="8"/>
+      <c r="AV20" s="8">
+        <v>109</v>
+      </c>
     </row>
     <row r="21" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
@@ -3719,7 +3753,9 @@
       <c r="AU21" s="8">
         <v>120</v>
       </c>
-      <c r="AV21" s="8"/>
+      <c r="AV21" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
@@ -3863,7 +3899,9 @@
       <c r="AU22" s="8">
         <v>95</v>
       </c>
-      <c r="AV22" s="8"/>
+      <c r="AV22" s="8">
+        <v>77</v>
+      </c>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
@@ -4007,7 +4045,9 @@
       <c r="AU23" s="8">
         <v>112</v>
       </c>
-      <c r="AV23" s="8"/>
+      <c r="AV23" s="8">
+        <v>112</v>
+      </c>
     </row>
     <row r="24" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
@@ -4151,7 +4191,9 @@
       <c r="AU24" s="8">
         <v>126</v>
       </c>
-      <c r="AV24" s="8"/>
+      <c r="AV24" s="8">
+        <v>122</v>
+      </c>
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
@@ -4295,7 +4337,9 @@
       <c r="AU25" s="8">
         <v>124</v>
       </c>
-      <c r="AV25" s="8"/>
+      <c r="AV25" s="8">
+        <v>122</v>
+      </c>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
@@ -4439,7 +4483,9 @@
       <c r="AU26" s="8">
         <v>107</v>
       </c>
-      <c r="AV26" s="8"/>
+      <c r="AV26" s="8">
+        <v>108</v>
+      </c>
     </row>
     <row r="27" spans="1:49" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
@@ -4631,9 +4677,9 @@
       </c>
       <c r="AV27" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AW27" s="19"/>
+        <v>2252</v>
+      </c>
+      <c r="AW27" s="18"/>
     </row>
     <row r="28" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F28" s="13"/>

--- a/2026 pasta satış.xlsx
+++ b/2026 pasta satış.xlsx
@@ -310,7 +310,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -342,22 +342,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -400,7 +389,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -684,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AW54"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.140625" bestFit="1" customWidth="1"/>
@@ -701,7 +689,7 @@
     <col min="36" max="36" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" s="4" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" s="4" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3" t="s">
@@ -842,8 +830,12 @@
       <c r="AV1" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="2" spans="1:48" ht="21" x14ac:dyDescent="0.25">
+      <c r="AW1" s="3"/>
+      <c r="AX1" s="3"/>
+      <c r="AY1" s="3"/>
+      <c r="AZ1" s="3"/>
+    </row>
+    <row r="2" spans="1:52" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="6">
         <v>46265</v>
@@ -986,8 +978,20 @@
       <c r="AV2" s="6">
         <v>46311</v>
       </c>
-    </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW2" s="6">
+        <v>46312</v>
+      </c>
+      <c r="AX2" s="6">
+        <v>46313</v>
+      </c>
+      <c r="AY2" s="6">
+        <v>46314</v>
+      </c>
+      <c r="AZ2" s="6">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>32</v>
       </c>
@@ -1087,11 +1091,11 @@
       <c r="AG3" s="8">
         <v>116</v>
       </c>
-      <c r="AH3" s="19" t="s">
+      <c r="AH3" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="AI3" s="19"/>
-      <c r="AJ3" s="19"/>
+      <c r="AI3" s="18"/>
+      <c r="AJ3" s="18"/>
       <c r="AK3" s="8">
         <v>0</v>
       </c>
@@ -1128,8 +1132,14 @@
       <c r="AV3" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="8"/>
+      <c r="AY3" s="8"/>
+      <c r="AZ3" s="8"/>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>34</v>
       </c>
@@ -1274,8 +1284,14 @@
       <c r="AV4" s="8">
         <v>134</v>
       </c>
-    </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW4" s="8">
+        <v>1</v>
+      </c>
+      <c r="AX4" s="8"/>
+      <c r="AY4" s="8"/>
+      <c r="AZ4" s="8"/>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1420,8 +1436,14 @@
       <c r="AV5" s="8">
         <v>78</v>
       </c>
-    </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX5" s="8"/>
+      <c r="AY5" s="8"/>
+      <c r="AZ5" s="8"/>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>36</v>
       </c>
@@ -1566,8 +1588,14 @@
       <c r="AV6" s="8">
         <v>61</v>
       </c>
-    </row>
-    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="8"/>
+      <c r="AY6" s="8"/>
+      <c r="AZ6" s="8"/>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>37</v>
       </c>
@@ -1712,8 +1740,14 @@
       <c r="AV7" s="8">
         <v>125</v>
       </c>
-    </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="8"/>
+      <c r="AY7" s="8"/>
+      <c r="AZ7" s="8"/>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>38</v>
       </c>
@@ -1858,8 +1892,14 @@
       <c r="AV8" s="8">
         <v>125</v>
       </c>
-    </row>
-    <row r="9" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="8"/>
+      <c r="AY8" s="8"/>
+      <c r="AZ8" s="8"/>
+    </row>
+    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>39</v>
       </c>
@@ -2004,8 +2044,14 @@
       <c r="AV9" s="8">
         <v>92</v>
       </c>
-    </row>
-    <row r="10" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="8"/>
+      <c r="AY9" s="8"/>
+      <c r="AZ9" s="8"/>
+    </row>
+    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>40</v>
       </c>
@@ -2150,8 +2196,14 @@
       <c r="AV10" s="8">
         <v>110</v>
       </c>
-    </row>
-    <row r="11" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="8"/>
+      <c r="AY10" s="8"/>
+      <c r="AZ10" s="8"/>
+    </row>
+    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
@@ -2296,8 +2348,14 @@
       <c r="AV11" s="8">
         <v>67</v>
       </c>
-    </row>
-    <row r="12" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="8"/>
+      <c r="AY11" s="8"/>
+      <c r="AZ11" s="8"/>
+    </row>
+    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -2442,8 +2500,14 @@
       <c r="AV12" s="8">
         <v>64</v>
       </c>
-    </row>
-    <row r="13" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="8"/>
+      <c r="AY12" s="8"/>
+      <c r="AZ12" s="8"/>
+    </row>
+    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>43</v>
       </c>
@@ -2588,8 +2652,14 @@
       <c r="AV13" s="8">
         <v>137</v>
       </c>
-    </row>
-    <row r="14" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW13" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX13" s="8"/>
+      <c r="AY13" s="8"/>
+      <c r="AZ13" s="8"/>
+    </row>
+    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>44</v>
       </c>
@@ -2734,8 +2804,14 @@
       <c r="AV14" s="8">
         <v>122</v>
       </c>
-    </row>
-    <row r="15" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW14" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="8"/>
+      <c r="AY14" s="8"/>
+      <c r="AZ14" s="8"/>
+    </row>
+    <row r="15" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>45</v>
       </c>
@@ -2880,8 +2956,14 @@
       <c r="AV15" s="8">
         <v>125</v>
       </c>
-    </row>
-    <row r="16" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW15" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX15" s="8"/>
+      <c r="AY15" s="8"/>
+      <c r="AZ15" s="8"/>
+    </row>
+    <row r="16" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -3026,8 +3108,14 @@
       <c r="AV16" s="8">
         <v>86</v>
       </c>
-    </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW16" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX16" s="8"/>
+      <c r="AY16" s="8"/>
+      <c r="AZ16" s="8"/>
+    </row>
+    <row r="17" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>47</v>
       </c>
@@ -3172,8 +3260,14 @@
       <c r="AV17" s="8">
         <v>84</v>
       </c>
-    </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW17" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX17" s="8"/>
+      <c r="AY17" s="8"/>
+      <c r="AZ17" s="8"/>
+    </row>
+    <row r="18" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>48</v>
       </c>
@@ -3318,8 +3412,14 @@
       <c r="AV18" s="8">
         <v>43</v>
       </c>
-    </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW18" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX18" s="8"/>
+      <c r="AY18" s="8"/>
+      <c r="AZ18" s="8"/>
+    </row>
+    <row r="19" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>49</v>
       </c>
@@ -3464,8 +3564,14 @@
       <c r="AV19" s="8">
         <v>49</v>
       </c>
-    </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW19" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX19" s="8"/>
+      <c r="AY19" s="8"/>
+      <c r="AZ19" s="8"/>
+    </row>
+    <row r="20" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>50</v>
       </c>
@@ -3610,8 +3716,14 @@
       <c r="AV20" s="8">
         <v>109</v>
       </c>
-    </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW20" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX20" s="8"/>
+      <c r="AY20" s="8"/>
+      <c r="AZ20" s="8"/>
+    </row>
+    <row r="21" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -3756,8 +3868,14 @@
       <c r="AV21" s="8">
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW21" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX21" s="8"/>
+      <c r="AY21" s="8"/>
+      <c r="AZ21" s="8"/>
+    </row>
+    <row r="22" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>52</v>
       </c>
@@ -3902,8 +4020,14 @@
       <c r="AV22" s="8">
         <v>77</v>
       </c>
-    </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW22" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX22" s="8"/>
+      <c r="AY22" s="8"/>
+      <c r="AZ22" s="8"/>
+    </row>
+    <row r="23" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>53</v>
       </c>
@@ -4048,8 +4172,14 @@
       <c r="AV23" s="8">
         <v>112</v>
       </c>
-    </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW23" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX23" s="8"/>
+      <c r="AY23" s="8"/>
+      <c r="AZ23" s="8"/>
+    </row>
+    <row r="24" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>54</v>
       </c>
@@ -4194,8 +4324,14 @@
       <c r="AV24" s="8">
         <v>122</v>
       </c>
-    </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW24" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX24" s="8"/>
+      <c r="AY24" s="8"/>
+      <c r="AZ24" s="8"/>
+    </row>
+    <row r="25" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>55</v>
       </c>
@@ -4340,8 +4476,14 @@
       <c r="AV25" s="8">
         <v>122</v>
       </c>
-    </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX25" s="8"/>
+      <c r="AY25" s="8"/>
+      <c r="AZ25" s="8"/>
+    </row>
+    <row r="26" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>56</v>
       </c>
@@ -4486,8 +4628,14 @@
       <c r="AV26" s="8">
         <v>108</v>
       </c>
-    </row>
-    <row r="27" spans="1:49" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AW26" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX26" s="8"/>
+      <c r="AY26" s="8"/>
+      <c r="AZ26" s="8"/>
+    </row>
+    <row r="27" spans="1:52" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>57</v>
       </c>
@@ -4580,7 +4728,7 @@
         <v>1484</v>
       </c>
       <c r="X27" s="12">
-        <f t="shared" ref="X27:AV27" si="3">SUM(X3:X26)</f>
+        <f t="shared" ref="X27:AZ27" si="3">SUM(X3:X26)</f>
         <v>1474</v>
       </c>
       <c r="Y27" s="12">
@@ -4679,13 +4827,28 @@
         <f t="shared" si="3"/>
         <v>2252</v>
       </c>
-      <c r="AW27" s="18"/>
-    </row>
-    <row r="28" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AW27" s="10">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AX27" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AY27" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AZ27" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F28" s="13"/>
       <c r="U28" s="14"/>
     </row>
-    <row r="29" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
       <c r="X29" s="15"/>
@@ -4695,7 +4858,7 @@
       <c r="AB29" s="15"/>
       <c r="AC29" s="15"/>
     </row>
-    <row r="30" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F30" s="13"/>
       <c r="G30" s="13"/>
       <c r="V30" s="13"/>
@@ -4708,7 +4871,7 @@
       <c r="AI30" s="13"/>
       <c r="AJ30" s="13"/>
     </row>
-    <row r="31" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F31" s="13"/>
       <c r="G31" s="13"/>
       <c r="V31" s="13"/>
@@ -4721,7 +4884,7 @@
       <c r="AI31" s="13"/>
       <c r="AJ31" s="13"/>
     </row>
-    <row r="32" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F32" s="13"/>
       <c r="G32" s="13"/>
       <c r="V32" s="13"/>

--- a/2026 pasta satış.xlsx
+++ b/2026 pasta satış.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="68">
   <si>
     <t>30°C – Açık</t>
   </si>
@@ -219,6 +219,16 @@
   </si>
   <si>
     <t>19°C – Yer yer sağanak yağışlı</t>
+  </si>
+  <si>
+    <t>17°C –
+Kısmen Güneşli</t>
+  </si>
+  <si>
+    <t>17 Ekim: 14°C - hafif yağmurlu</t>
+  </si>
+  <si>
+    <t>18 Ekim: 18°C - bulutlu</t>
   </si>
 </sst>
 </file>
@@ -830,9 +840,15 @@
       <c r="AV1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="AW1" s="3"/>
-      <c r="AX1" s="3"/>
-      <c r="AY1" s="3"/>
+      <c r="AW1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AY1" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="AZ1" s="3"/>
     </row>
     <row r="2" spans="1:52" ht="21" x14ac:dyDescent="0.25">
@@ -1135,8 +1151,12 @@
       <c r="AW3" s="8">
         <v>0</v>
       </c>
-      <c r="AX3" s="8"/>
-      <c r="AY3" s="8"/>
+      <c r="AX3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="8">
+        <v>0</v>
+      </c>
       <c r="AZ3" s="8"/>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.25">
@@ -1287,8 +1307,12 @@
       <c r="AW4" s="8">
         <v>1</v>
       </c>
-      <c r="AX4" s="8"/>
-      <c r="AY4" s="8"/>
+      <c r="AX4" s="8">
+        <v>131</v>
+      </c>
+      <c r="AY4" s="8">
+        <v>100</v>
+      </c>
       <c r="AZ4" s="8"/>
     </row>
     <row r="5" spans="1:52" x14ac:dyDescent="0.25">
@@ -1439,8 +1463,12 @@
       <c r="AW5" s="8">
         <v>0</v>
       </c>
-      <c r="AX5" s="8"/>
-      <c r="AY5" s="8"/>
+      <c r="AX5" s="8">
+        <v>62</v>
+      </c>
+      <c r="AY5" s="8">
+        <v>48</v>
+      </c>
       <c r="AZ5" s="8"/>
     </row>
     <row r="6" spans="1:52" x14ac:dyDescent="0.25">
@@ -1591,8 +1619,12 @@
       <c r="AW6" s="8">
         <v>0</v>
       </c>
-      <c r="AX6" s="8"/>
-      <c r="AY6" s="8"/>
+      <c r="AX6" s="8">
+        <v>74</v>
+      </c>
+      <c r="AY6" s="8">
+        <v>48</v>
+      </c>
       <c r="AZ6" s="8"/>
     </row>
     <row r="7" spans="1:52" x14ac:dyDescent="0.25">
@@ -1743,8 +1775,12 @@
       <c r="AW7" s="8">
         <v>0</v>
       </c>
-      <c r="AX7" s="8"/>
-      <c r="AY7" s="8"/>
+      <c r="AX7" s="8">
+        <v>117</v>
+      </c>
+      <c r="AY7" s="8">
+        <v>108</v>
+      </c>
       <c r="AZ7" s="8"/>
     </row>
     <row r="8" spans="1:52" x14ac:dyDescent="0.25">
@@ -1895,8 +1931,12 @@
       <c r="AW8" s="8">
         <v>0</v>
       </c>
-      <c r="AX8" s="8"/>
-      <c r="AY8" s="8"/>
+      <c r="AX8" s="8">
+        <v>122</v>
+      </c>
+      <c r="AY8" s="8">
+        <v>130</v>
+      </c>
       <c r="AZ8" s="8"/>
     </row>
     <row r="9" spans="1:52" x14ac:dyDescent="0.25">
@@ -2047,8 +2087,12 @@
       <c r="AW9" s="8">
         <v>0</v>
       </c>
-      <c r="AX9" s="8"/>
-      <c r="AY9" s="8"/>
+      <c r="AX9" s="8">
+        <v>92</v>
+      </c>
+      <c r="AY9" s="8">
+        <v>84</v>
+      </c>
       <c r="AZ9" s="8"/>
     </row>
     <row r="10" spans="1:52" x14ac:dyDescent="0.25">
@@ -2199,8 +2243,12 @@
       <c r="AW10" s="8">
         <v>0</v>
       </c>
-      <c r="AX10" s="8"/>
-      <c r="AY10" s="8"/>
+      <c r="AX10" s="8">
+        <v>110</v>
+      </c>
+      <c r="AY10" s="8">
+        <v>94</v>
+      </c>
       <c r="AZ10" s="8"/>
     </row>
     <row r="11" spans="1:52" x14ac:dyDescent="0.25">
@@ -2351,8 +2399,12 @@
       <c r="AW11" s="8">
         <v>0</v>
       </c>
-      <c r="AX11" s="8"/>
-      <c r="AY11" s="8"/>
+      <c r="AX11" s="8">
+        <v>45</v>
+      </c>
+      <c r="AY11" s="8">
+        <v>44</v>
+      </c>
       <c r="AZ11" s="8"/>
     </row>
     <row r="12" spans="1:52" x14ac:dyDescent="0.25">
@@ -2503,8 +2555,12 @@
       <c r="AW12" s="8">
         <v>0</v>
       </c>
-      <c r="AX12" s="8"/>
-      <c r="AY12" s="8"/>
+      <c r="AX12" s="8">
+        <v>63</v>
+      </c>
+      <c r="AY12" s="8">
+        <v>47</v>
+      </c>
       <c r="AZ12" s="8"/>
     </row>
     <row r="13" spans="1:52" x14ac:dyDescent="0.25">
@@ -2655,8 +2711,12 @@
       <c r="AW13" s="8">
         <v>0</v>
       </c>
-      <c r="AX13" s="8"/>
-      <c r="AY13" s="8"/>
+      <c r="AX13" s="8">
+        <v>116</v>
+      </c>
+      <c r="AY13" s="8">
+        <v>113</v>
+      </c>
       <c r="AZ13" s="8"/>
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.25">
@@ -2807,8 +2867,12 @@
       <c r="AW14" s="8">
         <v>0</v>
       </c>
-      <c r="AX14" s="8"/>
-      <c r="AY14" s="8"/>
+      <c r="AX14" s="8">
+        <v>96</v>
+      </c>
+      <c r="AY14" s="8">
+        <v>101</v>
+      </c>
       <c r="AZ14" s="8"/>
     </row>
     <row r="15" spans="1:52" x14ac:dyDescent="0.25">
@@ -2959,8 +3023,12 @@
       <c r="AW15" s="8">
         <v>0</v>
       </c>
-      <c r="AX15" s="8"/>
-      <c r="AY15" s="8"/>
+      <c r="AX15" s="8">
+        <v>120</v>
+      </c>
+      <c r="AY15" s="8">
+        <v>110</v>
+      </c>
       <c r="AZ15" s="8"/>
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.25">
@@ -3111,8 +3179,12 @@
       <c r="AW16" s="8">
         <v>0</v>
       </c>
-      <c r="AX16" s="8"/>
-      <c r="AY16" s="8"/>
+      <c r="AX16" s="8">
+        <v>79</v>
+      </c>
+      <c r="AY16" s="8">
+        <v>75</v>
+      </c>
       <c r="AZ16" s="8"/>
     </row>
     <row r="17" spans="1:52" x14ac:dyDescent="0.25">
@@ -3263,8 +3335,12 @@
       <c r="AW17" s="8">
         <v>0</v>
       </c>
-      <c r="AX17" s="8"/>
-      <c r="AY17" s="8"/>
+      <c r="AX17" s="8">
+        <v>86</v>
+      </c>
+      <c r="AY17" s="8">
+        <v>85</v>
+      </c>
       <c r="AZ17" s="8"/>
     </row>
     <row r="18" spans="1:52" x14ac:dyDescent="0.25">
@@ -3415,8 +3491,12 @@
       <c r="AW18" s="8">
         <v>0</v>
       </c>
-      <c r="AX18" s="8"/>
-      <c r="AY18" s="8"/>
+      <c r="AX18" s="8">
+        <v>43</v>
+      </c>
+      <c r="AY18" s="8">
+        <v>37</v>
+      </c>
       <c r="AZ18" s="8"/>
     </row>
     <row r="19" spans="1:52" x14ac:dyDescent="0.25">
@@ -3567,8 +3647,12 @@
       <c r="AW19" s="8">
         <v>0</v>
       </c>
-      <c r="AX19" s="8"/>
-      <c r="AY19" s="8"/>
+      <c r="AX19" s="8">
+        <v>41</v>
+      </c>
+      <c r="AY19" s="8">
+        <v>36</v>
+      </c>
       <c r="AZ19" s="8"/>
     </row>
     <row r="20" spans="1:52" x14ac:dyDescent="0.25">
@@ -3719,8 +3803,12 @@
       <c r="AW20" s="8">
         <v>0</v>
       </c>
-      <c r="AX20" s="8"/>
-      <c r="AY20" s="8"/>
+      <c r="AX20" s="8">
+        <v>95</v>
+      </c>
+      <c r="AY20" s="8">
+        <v>92</v>
+      </c>
       <c r="AZ20" s="8"/>
     </row>
     <row r="21" spans="1:52" x14ac:dyDescent="0.25">
@@ -3871,8 +3959,12 @@
       <c r="AW21" s="8">
         <v>0</v>
       </c>
-      <c r="AX21" s="8"/>
-      <c r="AY21" s="8"/>
+      <c r="AX21" s="8">
+        <v>105</v>
+      </c>
+      <c r="AY21" s="8">
+        <v>99</v>
+      </c>
       <c r="AZ21" s="8"/>
     </row>
     <row r="22" spans="1:52" x14ac:dyDescent="0.25">
@@ -4023,8 +4115,12 @@
       <c r="AW22" s="8">
         <v>0</v>
       </c>
-      <c r="AX22" s="8"/>
-      <c r="AY22" s="8"/>
+      <c r="AX22" s="8">
+        <v>70</v>
+      </c>
+      <c r="AY22" s="8">
+        <v>66</v>
+      </c>
       <c r="AZ22" s="8"/>
     </row>
     <row r="23" spans="1:52" x14ac:dyDescent="0.25">
@@ -4175,8 +4271,12 @@
       <c r="AW23" s="8">
         <v>0</v>
       </c>
-      <c r="AX23" s="8"/>
-      <c r="AY23" s="8"/>
+      <c r="AX23" s="8">
+        <v>81</v>
+      </c>
+      <c r="AY23" s="8">
+        <v>99</v>
+      </c>
       <c r="AZ23" s="8"/>
     </row>
     <row r="24" spans="1:52" x14ac:dyDescent="0.25">
@@ -4327,8 +4427,12 @@
       <c r="AW24" s="8">
         <v>0</v>
       </c>
-      <c r="AX24" s="8"/>
-      <c r="AY24" s="8"/>
+      <c r="AX24" s="8">
+        <v>131</v>
+      </c>
+      <c r="AY24" s="8">
+        <v>116</v>
+      </c>
       <c r="AZ24" s="8"/>
     </row>
     <row r="25" spans="1:52" x14ac:dyDescent="0.25">
@@ -4479,8 +4583,12 @@
       <c r="AW25" s="8">
         <v>0</v>
       </c>
-      <c r="AX25" s="8"/>
-      <c r="AY25" s="8"/>
+      <c r="AX25" s="8">
+        <v>120</v>
+      </c>
+      <c r="AY25" s="8">
+        <v>109</v>
+      </c>
       <c r="AZ25" s="8"/>
     </row>
     <row r="26" spans="1:52" x14ac:dyDescent="0.25">
@@ -4631,8 +4739,12 @@
       <c r="AW26" s="8">
         <v>0</v>
       </c>
-      <c r="AX26" s="8"/>
-      <c r="AY26" s="8"/>
+      <c r="AX26" s="8">
+        <v>101</v>
+      </c>
+      <c r="AY26" s="8">
+        <v>97</v>
+      </c>
       <c r="AZ26" s="8"/>
     </row>
     <row r="27" spans="1:52" ht="18.75" x14ac:dyDescent="0.3">
@@ -4833,11 +4945,11 @@
       </c>
       <c r="AX27" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="AY27" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1938</v>
       </c>
       <c r="AZ27" s="10">
         <f t="shared" si="3"/>

--- a/2026 pasta satış.xlsx
+++ b/2026 pasta satış.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
   <si>
     <t>30°C – Açık</t>
   </si>
@@ -849,7 +849,9 @@
       <c r="AY1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AZ1" s="3"/>
+      <c r="AZ1" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="2" spans="1:52" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
@@ -1157,7 +1159,9 @@
       <c r="AY3" s="8">
         <v>0</v>
       </c>
-      <c r="AZ3" s="8"/>
+      <c r="AZ3" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
@@ -1313,7 +1317,9 @@
       <c r="AY4" s="8">
         <v>100</v>
       </c>
-      <c r="AZ4" s="8"/>
+      <c r="AZ4" s="8">
+        <v>85</v>
+      </c>
     </row>
     <row r="5" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -1469,7 +1475,9 @@
       <c r="AY5" s="8">
         <v>48</v>
       </c>
-      <c r="AZ5" s="8"/>
+      <c r="AZ5" s="8">
+        <v>41</v>
+      </c>
     </row>
     <row r="6" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -1625,7 +1633,9 @@
       <c r="AY6" s="8">
         <v>48</v>
       </c>
-      <c r="AZ6" s="8"/>
+      <c r="AZ6" s="8">
+        <v>39</v>
+      </c>
     </row>
     <row r="7" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -1781,7 +1791,9 @@
       <c r="AY7" s="8">
         <v>108</v>
       </c>
-      <c r="AZ7" s="8"/>
+      <c r="AZ7" s="8">
+        <v>89</v>
+      </c>
     </row>
     <row r="8" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
@@ -1937,7 +1949,9 @@
       <c r="AY8" s="8">
         <v>130</v>
       </c>
-      <c r="AZ8" s="8"/>
+      <c r="AZ8" s="8">
+        <v>87</v>
+      </c>
     </row>
     <row r="9" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
@@ -2093,7 +2107,9 @@
       <c r="AY9" s="8">
         <v>84</v>
       </c>
-      <c r="AZ9" s="8"/>
+      <c r="AZ9" s="8">
+        <v>46</v>
+      </c>
     </row>
     <row r="10" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
@@ -2249,7 +2265,9 @@
       <c r="AY10" s="8">
         <v>94</v>
       </c>
-      <c r="AZ10" s="8"/>
+      <c r="AZ10" s="8">
+        <v>90</v>
+      </c>
     </row>
     <row r="11" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
@@ -2405,7 +2423,9 @@
       <c r="AY11" s="8">
         <v>44</v>
       </c>
-      <c r="AZ11" s="8"/>
+      <c r="AZ11" s="8">
+        <v>55</v>
+      </c>
     </row>
     <row r="12" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
@@ -2561,7 +2581,9 @@
       <c r="AY12" s="8">
         <v>47</v>
       </c>
-      <c r="AZ12" s="8"/>
+      <c r="AZ12" s="8">
+        <v>36</v>
+      </c>
     </row>
     <row r="13" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
@@ -2717,7 +2739,9 @@
       <c r="AY13" s="8">
         <v>113</v>
       </c>
-      <c r="AZ13" s="8"/>
+      <c r="AZ13" s="8">
+        <v>85</v>
+      </c>
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
@@ -2873,7 +2897,9 @@
       <c r="AY14" s="8">
         <v>101</v>
       </c>
-      <c r="AZ14" s="8"/>
+      <c r="AZ14" s="8">
+        <v>72</v>
+      </c>
     </row>
     <row r="15" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
@@ -3029,7 +3055,9 @@
       <c r="AY15" s="8">
         <v>110</v>
       </c>
-      <c r="AZ15" s="8"/>
+      <c r="AZ15" s="8">
+        <v>107</v>
+      </c>
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
@@ -3185,7 +3213,9 @@
       <c r="AY16" s="8">
         <v>75</v>
       </c>
-      <c r="AZ16" s="8"/>
+      <c r="AZ16" s="8">
+        <v>63</v>
+      </c>
     </row>
     <row r="17" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
@@ -3341,7 +3371,9 @@
       <c r="AY17" s="8">
         <v>85</v>
       </c>
-      <c r="AZ17" s="8"/>
+      <c r="AZ17" s="8">
+        <v>79</v>
+      </c>
     </row>
     <row r="18" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
@@ -3497,7 +3529,9 @@
       <c r="AY18" s="8">
         <v>37</v>
       </c>
-      <c r="AZ18" s="8"/>
+      <c r="AZ18" s="8">
+        <v>34</v>
+      </c>
     </row>
     <row r="19" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
@@ -3653,7 +3687,9 @@
       <c r="AY19" s="8">
         <v>36</v>
       </c>
-      <c r="AZ19" s="8"/>
+      <c r="AZ19" s="8">
+        <v>40</v>
+      </c>
     </row>
     <row r="20" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
@@ -3809,7 +3845,9 @@
       <c r="AY20" s="8">
         <v>92</v>
       </c>
-      <c r="AZ20" s="8"/>
+      <c r="AZ20" s="8">
+        <v>79</v>
+      </c>
     </row>
     <row r="21" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
@@ -3965,7 +4003,9 @@
       <c r="AY21" s="8">
         <v>99</v>
       </c>
-      <c r="AZ21" s="8"/>
+      <c r="AZ21" s="8">
+        <v>88</v>
+      </c>
     </row>
     <row r="22" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
@@ -4121,7 +4161,9 @@
       <c r="AY22" s="8">
         <v>66</v>
       </c>
-      <c r="AZ22" s="8"/>
+      <c r="AZ22" s="8">
+        <v>47</v>
+      </c>
     </row>
     <row r="23" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
@@ -4277,7 +4319,9 @@
       <c r="AY23" s="8">
         <v>99</v>
       </c>
-      <c r="AZ23" s="8"/>
+      <c r="AZ23" s="8">
+        <v>79</v>
+      </c>
     </row>
     <row r="24" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
@@ -4433,7 +4477,9 @@
       <c r="AY24" s="8">
         <v>116</v>
       </c>
-      <c r="AZ24" s="8"/>
+      <c r="AZ24" s="8">
+        <v>77</v>
+      </c>
     </row>
     <row r="25" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
@@ -4589,7 +4635,9 @@
       <c r="AY25" s="8">
         <v>109</v>
       </c>
-      <c r="AZ25" s="8"/>
+      <c r="AZ25" s="8">
+        <v>79</v>
+      </c>
     </row>
     <row r="26" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
@@ -4745,7 +4793,9 @@
       <c r="AY26" s="8">
         <v>97</v>
       </c>
-      <c r="AZ26" s="8"/>
+      <c r="AZ26" s="8">
+        <v>92</v>
+      </c>
     </row>
     <row r="27" spans="1:52" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
@@ -4953,7 +5003,7 @@
       </c>
       <c r="AZ27" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="28" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">

--- a/2026 pasta satış.xlsx
+++ b/2026 pasta satış.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="70">
   <si>
     <t>30°C – Açık</t>
   </si>
@@ -229,6 +229,12 @@
   </si>
   <si>
     <t>18 Ekim: 18°C - bulutlu</t>
+  </si>
+  <si>
+    <t>19°C – Açık</t>
+  </si>
+  <si>
+    <t>17°C – Açık</t>
   </si>
 </sst>
 </file>
@@ -682,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AZ54"/>
+  <dimension ref="A1:BC54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.140625" bestFit="1" customWidth="1"/>
@@ -699,7 +705,7 @@
     <col min="36" max="36" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" s="4" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:55" s="4" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3" t="s">
@@ -850,10 +856,15 @@
         <v>65</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>27</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="BA1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="BB1" s="3"/>
+      <c r="BC1" s="3"/>
     </row>
-    <row r="2" spans="1:52" ht="21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:55" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="6">
         <v>46265</v>
@@ -1008,8 +1019,13 @@
       <c r="AZ2" s="6">
         <v>46315</v>
       </c>
+      <c r="BA2" s="6">
+        <v>46316</v>
+      </c>
+      <c r="BB2" s="6"/>
+      <c r="BC2" s="6"/>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>32</v>
       </c>
@@ -1162,8 +1178,13 @@
       <c r="AZ3" s="8">
         <v>0</v>
       </c>
+      <c r="BA3" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB3" s="8"/>
+      <c r="BC3" s="8"/>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>34</v>
       </c>
@@ -1320,8 +1341,13 @@
       <c r="AZ4" s="8">
         <v>85</v>
       </c>
+      <c r="BA4" s="8">
+        <v>104</v>
+      </c>
+      <c r="BB4" s="8"/>
+      <c r="BC4" s="8"/>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1478,8 +1504,13 @@
       <c r="AZ5" s="8">
         <v>41</v>
       </c>
+      <c r="BA5" s="8">
+        <v>52</v>
+      </c>
+      <c r="BB5" s="8"/>
+      <c r="BC5" s="8"/>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>36</v>
       </c>
@@ -1636,8 +1667,13 @@
       <c r="AZ6" s="8">
         <v>39</v>
       </c>
+      <c r="BA6" s="8">
+        <v>53</v>
+      </c>
+      <c r="BB6" s="8"/>
+      <c r="BC6" s="8"/>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>37</v>
       </c>
@@ -1794,8 +1830,13 @@
       <c r="AZ7" s="8">
         <v>89</v>
       </c>
+      <c r="BA7" s="8">
+        <v>118</v>
+      </c>
+      <c r="BB7" s="8"/>
+      <c r="BC7" s="8"/>
     </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>38</v>
       </c>
@@ -1952,8 +1993,13 @@
       <c r="AZ8" s="8">
         <v>87</v>
       </c>
+      <c r="BA8" s="8">
+        <v>119</v>
+      </c>
+      <c r="BB8" s="8"/>
+      <c r="BC8" s="8"/>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>39</v>
       </c>
@@ -2110,8 +2156,13 @@
       <c r="AZ9" s="8">
         <v>46</v>
       </c>
+      <c r="BA9" s="8">
+        <v>89</v>
+      </c>
+      <c r="BB9" s="8"/>
+      <c r="BC9" s="8"/>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>40</v>
       </c>
@@ -2268,8 +2319,13 @@
       <c r="AZ10" s="8">
         <v>90</v>
       </c>
+      <c r="BA10" s="8">
+        <v>111</v>
+      </c>
+      <c r="BB10" s="8"/>
+      <c r="BC10" s="8"/>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
@@ -2426,8 +2482,13 @@
       <c r="AZ11" s="8">
         <v>55</v>
       </c>
+      <c r="BA11" s="8">
+        <v>59</v>
+      </c>
+      <c r="BB11" s="8"/>
+      <c r="BC11" s="8"/>
     </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -2584,8 +2645,13 @@
       <c r="AZ12" s="8">
         <v>36</v>
       </c>
+      <c r="BA12" s="8">
+        <v>51</v>
+      </c>
+      <c r="BB12" s="8"/>
+      <c r="BC12" s="8"/>
     </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>43</v>
       </c>
@@ -2742,8 +2808,13 @@
       <c r="AZ13" s="8">
         <v>85</v>
       </c>
+      <c r="BA13" s="8">
+        <v>119</v>
+      </c>
+      <c r="BB13" s="8"/>
+      <c r="BC13" s="8"/>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>44</v>
       </c>
@@ -2900,8 +2971,13 @@
       <c r="AZ14" s="8">
         <v>72</v>
       </c>
+      <c r="BA14" s="8">
+        <v>111</v>
+      </c>
+      <c r="BB14" s="8"/>
+      <c r="BC14" s="8"/>
     </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>45</v>
       </c>
@@ -3058,8 +3134,13 @@
       <c r="AZ15" s="8">
         <v>107</v>
       </c>
+      <c r="BA15" s="8">
+        <v>119</v>
+      </c>
+      <c r="BB15" s="8"/>
+      <c r="BC15" s="8"/>
     </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -3216,8 +3297,13 @@
       <c r="AZ16" s="8">
         <v>63</v>
       </c>
+      <c r="BA16" s="8">
+        <v>94</v>
+      </c>
+      <c r="BB16" s="8"/>
+      <c r="BC16" s="8"/>
     </row>
-    <row r="17" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>47</v>
       </c>
@@ -3374,8 +3460,13 @@
       <c r="AZ17" s="8">
         <v>79</v>
       </c>
+      <c r="BA17" s="8">
+        <v>83</v>
+      </c>
+      <c r="BB17" s="8"/>
+      <c r="BC17" s="8"/>
     </row>
-    <row r="18" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>48</v>
       </c>
@@ -3532,8 +3623,13 @@
       <c r="AZ18" s="8">
         <v>34</v>
       </c>
+      <c r="BA18" s="8">
+        <v>37</v>
+      </c>
+      <c r="BB18" s="8"/>
+      <c r="BC18" s="8"/>
     </row>
-    <row r="19" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>49</v>
       </c>
@@ -3690,8 +3786,13 @@
       <c r="AZ19" s="8">
         <v>40</v>
       </c>
+      <c r="BA19" s="8">
+        <v>39</v>
+      </c>
+      <c r="BB19" s="8"/>
+      <c r="BC19" s="8"/>
     </row>
-    <row r="20" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>50</v>
       </c>
@@ -3848,8 +3949,13 @@
       <c r="AZ20" s="8">
         <v>79</v>
       </c>
+      <c r="BA20" s="8">
+        <v>107</v>
+      </c>
+      <c r="BB20" s="8"/>
+      <c r="BC20" s="8"/>
     </row>
-    <row r="21" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -4006,8 +4112,13 @@
       <c r="AZ21" s="8">
         <v>88</v>
       </c>
+      <c r="BA21" s="8">
+        <v>112</v>
+      </c>
+      <c r="BB21" s="8"/>
+      <c r="BC21" s="8"/>
     </row>
-    <row r="22" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>52</v>
       </c>
@@ -4164,8 +4275,13 @@
       <c r="AZ22" s="8">
         <v>47</v>
       </c>
+      <c r="BA22" s="8">
+        <v>69</v>
+      </c>
+      <c r="BB22" s="8"/>
+      <c r="BC22" s="8"/>
     </row>
-    <row r="23" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>53</v>
       </c>
@@ -4322,8 +4438,13 @@
       <c r="AZ23" s="8">
         <v>79</v>
       </c>
+      <c r="BA23" s="8">
+        <v>102</v>
+      </c>
+      <c r="BB23" s="8"/>
+      <c r="BC23" s="8"/>
     </row>
-    <row r="24" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>54</v>
       </c>
@@ -4480,8 +4601,13 @@
       <c r="AZ24" s="8">
         <v>77</v>
       </c>
+      <c r="BA24" s="8">
+        <v>106</v>
+      </c>
+      <c r="BB24" s="8"/>
+      <c r="BC24" s="8"/>
     </row>
-    <row r="25" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>55</v>
       </c>
@@ -4638,8 +4764,13 @@
       <c r="AZ25" s="8">
         <v>79</v>
       </c>
+      <c r="BA25" s="8">
+        <v>106</v>
+      </c>
+      <c r="BB25" s="8"/>
+      <c r="BC25" s="8"/>
     </row>
-    <row r="26" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>56</v>
       </c>
@@ -4796,8 +4927,13 @@
       <c r="AZ26" s="8">
         <v>92</v>
       </c>
+      <c r="BA26" s="8">
+        <v>93</v>
+      </c>
+      <c r="BB26" s="8"/>
+      <c r="BC26" s="8"/>
     </row>
-    <row r="27" spans="1:52" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:55" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>57</v>
       </c>
@@ -4890,7 +5026,7 @@
         <v>1484</v>
       </c>
       <c r="X27" s="12">
-        <f t="shared" ref="X27:AZ27" si="3">SUM(X3:X26)</f>
+        <f t="shared" ref="X27:BA27" si="3">SUM(X3:X26)</f>
         <v>1474</v>
       </c>
       <c r="Y27" s="12">
@@ -5005,12 +5141,18 @@
         <f t="shared" si="3"/>
         <v>1589</v>
       </c>
+      <c r="BA27" s="10">
+        <f t="shared" si="3"/>
+        <v>2053</v>
+      </c>
+      <c r="BB27" s="10"/>
+      <c r="BC27" s="10"/>
     </row>
-    <row r="28" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F28" s="13"/>
       <c r="U28" s="14"/>
     </row>
-    <row r="29" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
       <c r="X29" s="15"/>
@@ -5020,7 +5162,7 @@
       <c r="AB29" s="15"/>
       <c r="AC29" s="15"/>
     </row>
-    <row r="30" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F30" s="13"/>
       <c r="G30" s="13"/>
       <c r="V30" s="13"/>
@@ -5033,7 +5175,7 @@
       <c r="AI30" s="13"/>
       <c r="AJ30" s="13"/>
     </row>
-    <row r="31" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F31" s="13"/>
       <c r="G31" s="13"/>
       <c r="V31" s="13"/>
@@ -5046,7 +5188,7 @@
       <c r="AI31" s="13"/>
       <c r="AJ31" s="13"/>
     </row>
-    <row r="32" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F32" s="13"/>
       <c r="G32" s="13"/>
       <c r="V32" s="13"/>

--- a/2026 pasta satış.xlsx
+++ b/2026 pasta satış.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="71">
   <si>
     <t>30°C – Açık</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>17°C – Açık</t>
+  </si>
+  <si>
+    <t>22°C –Güneşli</t>
   </si>
 </sst>
 </file>
@@ -861,7 +864,9 @@
       <c r="BA1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="BB1" s="3"/>
+      <c r="BB1" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="BC1" s="3"/>
     </row>
     <row r="2" spans="1:55" ht="21" x14ac:dyDescent="0.25">
@@ -1022,7 +1027,9 @@
       <c r="BA2" s="6">
         <v>46316</v>
       </c>
-      <c r="BB2" s="6"/>
+      <c r="BB2" s="6">
+        <v>46317</v>
+      </c>
       <c r="BC2" s="6"/>
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.25">
@@ -1181,7 +1188,9 @@
       <c r="BA3" s="8">
         <v>0</v>
       </c>
-      <c r="BB3" s="8"/>
+      <c r="BB3" s="8">
+        <v>0</v>
+      </c>
       <c r="BC3" s="8"/>
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.25">
@@ -1344,7 +1353,9 @@
       <c r="BA4" s="8">
         <v>104</v>
       </c>
-      <c r="BB4" s="8"/>
+      <c r="BB4" s="8">
+        <v>92</v>
+      </c>
       <c r="BC4" s="8"/>
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.25">
@@ -1507,7 +1518,9 @@
       <c r="BA5" s="8">
         <v>52</v>
       </c>
-      <c r="BB5" s="8"/>
+      <c r="BB5" s="8">
+        <v>40</v>
+      </c>
       <c r="BC5" s="8"/>
     </row>
     <row r="6" spans="1:55" x14ac:dyDescent="0.25">
@@ -1670,7 +1683,9 @@
       <c r="BA6" s="8">
         <v>53</v>
       </c>
-      <c r="BB6" s="8"/>
+      <c r="BB6" s="8">
+        <v>41</v>
+      </c>
       <c r="BC6" s="8"/>
     </row>
     <row r="7" spans="1:55" x14ac:dyDescent="0.25">
@@ -1833,7 +1848,9 @@
       <c r="BA7" s="8">
         <v>118</v>
       </c>
-      <c r="BB7" s="8"/>
+      <c r="BB7" s="8">
+        <v>78</v>
+      </c>
       <c r="BC7" s="8"/>
     </row>
     <row r="8" spans="1:55" x14ac:dyDescent="0.25">
@@ -1996,7 +2013,9 @@
       <c r="BA8" s="8">
         <v>119</v>
       </c>
-      <c r="BB8" s="8"/>
+      <c r="BB8" s="8">
+        <v>91</v>
+      </c>
       <c r="BC8" s="8"/>
     </row>
     <row r="9" spans="1:55" x14ac:dyDescent="0.25">
@@ -2159,7 +2178,9 @@
       <c r="BA9" s="8">
         <v>89</v>
       </c>
-      <c r="BB9" s="8"/>
+      <c r="BB9" s="8">
+        <v>69</v>
+      </c>
       <c r="BC9" s="8"/>
     </row>
     <row r="10" spans="1:55" x14ac:dyDescent="0.25">
@@ -2322,7 +2343,9 @@
       <c r="BA10" s="8">
         <v>111</v>
       </c>
-      <c r="BB10" s="8"/>
+      <c r="BB10" s="8">
+        <v>81</v>
+      </c>
       <c r="BC10" s="8"/>
     </row>
     <row r="11" spans="1:55" x14ac:dyDescent="0.25">
@@ -2485,7 +2508,9 @@
       <c r="BA11" s="8">
         <v>59</v>
       </c>
-      <c r="BB11" s="8"/>
+      <c r="BB11" s="8">
+        <v>49</v>
+      </c>
       <c r="BC11" s="8"/>
     </row>
     <row r="12" spans="1:55" x14ac:dyDescent="0.25">
@@ -2648,7 +2673,9 @@
       <c r="BA12" s="8">
         <v>51</v>
       </c>
-      <c r="BB12" s="8"/>
+      <c r="BB12" s="8">
+        <v>35</v>
+      </c>
       <c r="BC12" s="8"/>
     </row>
     <row r="13" spans="1:55" x14ac:dyDescent="0.25">
@@ -2811,7 +2838,9 @@
       <c r="BA13" s="8">
         <v>119</v>
       </c>
-      <c r="BB13" s="8"/>
+      <c r="BB13" s="8">
+        <v>76</v>
+      </c>
       <c r="BC13" s="8"/>
     </row>
     <row r="14" spans="1:55" x14ac:dyDescent="0.25">
@@ -2974,7 +3003,9 @@
       <c r="BA14" s="8">
         <v>111</v>
       </c>
-      <c r="BB14" s="8"/>
+      <c r="BB14" s="8">
+        <v>83</v>
+      </c>
       <c r="BC14" s="8"/>
     </row>
     <row r="15" spans="1:55" x14ac:dyDescent="0.25">
@@ -3137,7 +3168,9 @@
       <c r="BA15" s="8">
         <v>119</v>
       </c>
-      <c r="BB15" s="8"/>
+      <c r="BB15" s="8">
+        <v>102</v>
+      </c>
       <c r="BC15" s="8"/>
     </row>
     <row r="16" spans="1:55" x14ac:dyDescent="0.25">
@@ -3300,7 +3333,9 @@
       <c r="BA16" s="8">
         <v>94</v>
       </c>
-      <c r="BB16" s="8"/>
+      <c r="BB16" s="8">
+        <v>56</v>
+      </c>
       <c r="BC16" s="8"/>
     </row>
     <row r="17" spans="1:55" x14ac:dyDescent="0.25">
@@ -3463,7 +3498,9 @@
       <c r="BA17" s="8">
         <v>83</v>
       </c>
-      <c r="BB17" s="8"/>
+      <c r="BB17" s="8">
+        <v>76</v>
+      </c>
       <c r="BC17" s="8"/>
     </row>
     <row r="18" spans="1:55" x14ac:dyDescent="0.25">
@@ -3626,7 +3663,9 @@
       <c r="BA18" s="8">
         <v>37</v>
       </c>
-      <c r="BB18" s="8"/>
+      <c r="BB18" s="8">
+        <v>43</v>
+      </c>
       <c r="BC18" s="8"/>
     </row>
     <row r="19" spans="1:55" x14ac:dyDescent="0.25">
@@ -3789,7 +3828,9 @@
       <c r="BA19" s="8">
         <v>39</v>
       </c>
-      <c r="BB19" s="8"/>
+      <c r="BB19" s="8">
+        <v>39</v>
+      </c>
       <c r="BC19" s="8"/>
     </row>
     <row r="20" spans="1:55" x14ac:dyDescent="0.25">
@@ -3952,7 +3993,9 @@
       <c r="BA20" s="8">
         <v>107</v>
       </c>
-      <c r="BB20" s="8"/>
+      <c r="BB20" s="8">
+        <v>85</v>
+      </c>
       <c r="BC20" s="8"/>
     </row>
     <row r="21" spans="1:55" x14ac:dyDescent="0.25">
@@ -4115,7 +4158,9 @@
       <c r="BA21" s="8">
         <v>112</v>
       </c>
-      <c r="BB21" s="8"/>
+      <c r="BB21" s="8">
+        <v>94</v>
+      </c>
       <c r="BC21" s="8"/>
     </row>
     <row r="22" spans="1:55" x14ac:dyDescent="0.25">
@@ -4278,7 +4323,9 @@
       <c r="BA22" s="8">
         <v>69</v>
       </c>
-      <c r="BB22" s="8"/>
+      <c r="BB22" s="8">
+        <v>60</v>
+      </c>
       <c r="BC22" s="8"/>
     </row>
     <row r="23" spans="1:55" x14ac:dyDescent="0.25">
@@ -4441,7 +4488,9 @@
       <c r="BA23" s="8">
         <v>102</v>
       </c>
-      <c r="BB23" s="8"/>
+      <c r="BB23" s="8">
+        <v>69</v>
+      </c>
       <c r="BC23" s="8"/>
     </row>
     <row r="24" spans="1:55" x14ac:dyDescent="0.25">
@@ -4604,7 +4653,9 @@
       <c r="BA24" s="8">
         <v>106</v>
       </c>
-      <c r="BB24" s="8"/>
+      <c r="BB24" s="8">
+        <v>76</v>
+      </c>
       <c r="BC24" s="8"/>
     </row>
     <row r="25" spans="1:55" x14ac:dyDescent="0.25">
@@ -4767,7 +4818,9 @@
       <c r="BA25" s="8">
         <v>106</v>
       </c>
-      <c r="BB25" s="8"/>
+      <c r="BB25" s="8">
+        <v>75</v>
+      </c>
       <c r="BC25" s="8"/>
     </row>
     <row r="26" spans="1:55" x14ac:dyDescent="0.25">
@@ -4930,7 +4983,9 @@
       <c r="BA26" s="8">
         <v>93</v>
       </c>
-      <c r="BB26" s="8"/>
+      <c r="BB26" s="8">
+        <v>91</v>
+      </c>
       <c r="BC26" s="8"/>
     </row>
     <row r="27" spans="1:55" ht="18.75" x14ac:dyDescent="0.3">
@@ -5026,7 +5081,7 @@
         <v>1484</v>
       </c>
       <c r="X27" s="12">
-        <f t="shared" ref="X27:BA27" si="3">SUM(X3:X26)</f>
+        <f t="shared" ref="X27:BB27" si="3">SUM(X3:X26)</f>
         <v>1474</v>
       </c>
       <c r="Y27" s="12">
@@ -5145,7 +5200,10 @@
         <f t="shared" si="3"/>
         <v>2053</v>
       </c>
-      <c r="BB27" s="10"/>
+      <c r="BB27" s="10">
+        <f t="shared" si="3"/>
+        <v>1601</v>
+      </c>
       <c r="BC27" s="10"/>
     </row>
     <row r="28" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">

--- a/2026 pasta satış.xlsx
+++ b/2026 pasta satış.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="72">
   <si>
     <t>30°C – Açık</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>22°C –Güneşli</t>
+  </si>
+  <si>
+    <t>19°C –Güneşli</t>
   </si>
 </sst>
 </file>
@@ -867,7 +870,9 @@
       <c r="BB1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="BC1" s="3"/>
+      <c r="BC1" s="3" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="2" spans="1:55" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
@@ -1030,7 +1035,9 @@
       <c r="BB2" s="6">
         <v>46317</v>
       </c>
-      <c r="BC2" s="6"/>
+      <c r="BC2" s="6">
+        <v>46318</v>
+      </c>
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
@@ -1191,7 +1198,9 @@
       <c r="BB3" s="8">
         <v>0</v>
       </c>
-      <c r="BC3" s="8"/>
+      <c r="BC3" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
@@ -1356,7 +1365,9 @@
       <c r="BB4" s="8">
         <v>92</v>
       </c>
-      <c r="BC4" s="8"/>
+      <c r="BC4" s="8">
+        <v>108</v>
+      </c>
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -1521,7 +1532,9 @@
       <c r="BB5" s="8">
         <v>40</v>
       </c>
-      <c r="BC5" s="8"/>
+      <c r="BC5" s="8">
+        <v>34</v>
+      </c>
     </row>
     <row r="6" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -1686,7 +1699,9 @@
       <c r="BB6" s="8">
         <v>41</v>
       </c>
-      <c r="BC6" s="8"/>
+      <c r="BC6" s="8">
+        <v>36</v>
+      </c>
     </row>
     <row r="7" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -1851,7 +1866,9 @@
       <c r="BB7" s="8">
         <v>78</v>
       </c>
-      <c r="BC7" s="8"/>
+      <c r="BC7" s="8">
+        <v>88</v>
+      </c>
     </row>
     <row r="8" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
@@ -2016,7 +2033,9 @@
       <c r="BB8" s="8">
         <v>91</v>
       </c>
-      <c r="BC8" s="8"/>
+      <c r="BC8" s="8">
+        <v>125</v>
+      </c>
     </row>
     <row r="9" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
@@ -2181,7 +2200,9 @@
       <c r="BB9" s="8">
         <v>69</v>
       </c>
-      <c r="BC9" s="8"/>
+      <c r="BC9" s="8">
+        <v>99</v>
+      </c>
     </row>
     <row r="10" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
@@ -2346,7 +2367,9 @@
       <c r="BB10" s="8">
         <v>81</v>
       </c>
-      <c r="BC10" s="8"/>
+      <c r="BC10" s="8">
+        <v>77</v>
+      </c>
     </row>
     <row r="11" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
@@ -2511,7 +2534,9 @@
       <c r="BB11" s="8">
         <v>49</v>
       </c>
-      <c r="BC11" s="8"/>
+      <c r="BC11" s="8">
+        <v>33</v>
+      </c>
     </row>
     <row r="12" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
@@ -2676,7 +2701,9 @@
       <c r="BB12" s="8">
         <v>35</v>
       </c>
-      <c r="BC12" s="8"/>
+      <c r="BC12" s="8">
+        <v>38</v>
+      </c>
     </row>
     <row r="13" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
@@ -2841,7 +2868,9 @@
       <c r="BB13" s="8">
         <v>76</v>
       </c>
-      <c r="BC13" s="8"/>
+      <c r="BC13" s="8">
+        <v>116</v>
+      </c>
     </row>
     <row r="14" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
@@ -3006,7 +3035,9 @@
       <c r="BB14" s="8">
         <v>83</v>
       </c>
-      <c r="BC14" s="8"/>
+      <c r="BC14" s="8">
+        <v>116</v>
+      </c>
     </row>
     <row r="15" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
@@ -3171,7 +3202,9 @@
       <c r="BB15" s="8">
         <v>102</v>
       </c>
-      <c r="BC15" s="8"/>
+      <c r="BC15" s="8">
+        <v>125</v>
+      </c>
     </row>
     <row r="16" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
@@ -3336,7 +3369,9 @@
       <c r="BB16" s="8">
         <v>56</v>
       </c>
-      <c r="BC16" s="8"/>
+      <c r="BC16" s="8">
+        <v>69</v>
+      </c>
     </row>
     <row r="17" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
@@ -3501,7 +3536,9 @@
       <c r="BB17" s="8">
         <v>76</v>
       </c>
-      <c r="BC17" s="8"/>
+      <c r="BC17" s="8">
+        <v>70</v>
+      </c>
     </row>
     <row r="18" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
@@ -3666,7 +3703,9 @@
       <c r="BB18" s="8">
         <v>43</v>
       </c>
-      <c r="BC18" s="8"/>
+      <c r="BC18" s="8">
+        <v>35</v>
+      </c>
     </row>
     <row r="19" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
@@ -3831,7 +3870,9 @@
       <c r="BB19" s="8">
         <v>39</v>
       </c>
-      <c r="BC19" s="8"/>
+      <c r="BC19" s="8">
+        <v>33</v>
+      </c>
     </row>
     <row r="20" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
@@ -3996,7 +4037,9 @@
       <c r="BB20" s="8">
         <v>85</v>
       </c>
-      <c r="BC20" s="8"/>
+      <c r="BC20" s="8">
+        <v>125</v>
+      </c>
     </row>
     <row r="21" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
@@ -4161,7 +4204,9 @@
       <c r="BB21" s="8">
         <v>94</v>
       </c>
-      <c r="BC21" s="8"/>
+      <c r="BC21" s="8">
+        <v>96</v>
+      </c>
     </row>
     <row r="22" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
@@ -4326,7 +4371,9 @@
       <c r="BB22" s="8">
         <v>60</v>
       </c>
-      <c r="BC22" s="8"/>
+      <c r="BC22" s="8">
+        <v>62</v>
+      </c>
     </row>
     <row r="23" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
@@ -4491,7 +4538,9 @@
       <c r="BB23" s="8">
         <v>69</v>
       </c>
-      <c r="BC23" s="8"/>
+      <c r="BC23" s="8">
+        <v>72</v>
+      </c>
     </row>
     <row r="24" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
@@ -4656,7 +4705,9 @@
       <c r="BB24" s="8">
         <v>76</v>
       </c>
-      <c r="BC24" s="8"/>
+      <c r="BC24" s="8">
+        <v>96</v>
+      </c>
     </row>
     <row r="25" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
@@ -4821,7 +4872,9 @@
       <c r="BB25" s="8">
         <v>75</v>
       </c>
-      <c r="BC25" s="8"/>
+      <c r="BC25" s="8">
+        <v>96</v>
+      </c>
     </row>
     <row r="26" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
@@ -4986,7 +5039,9 @@
       <c r="BB26" s="8">
         <v>91</v>
       </c>
-      <c r="BC26" s="8"/>
+      <c r="BC26" s="8">
+        <v>69</v>
+      </c>
     </row>
     <row r="27" spans="1:55" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
@@ -5081,7 +5136,7 @@
         <v>1484</v>
       </c>
       <c r="X27" s="12">
-        <f t="shared" ref="X27:BB27" si="3">SUM(X3:X26)</f>
+        <f t="shared" ref="X27:BC27" si="3">SUM(X3:X26)</f>
         <v>1474</v>
       </c>
       <c r="Y27" s="12">
@@ -5204,7 +5259,10 @@
         <f t="shared" si="3"/>
         <v>1601</v>
       </c>
-      <c r="BC27" s="10"/>
+      <c r="BC27" s="10">
+        <f t="shared" si="3"/>
+        <v>1818</v>
+      </c>
     </row>
     <row r="28" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F28" s="13"/>

--- a/2026 pasta satış.xlsx
+++ b/2026 pasta satış.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="73">
   <si>
     <t>30°C – Açık</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>19°C –Güneşli</t>
+  </si>
+  <si>
+    <t>20°C –Güneşli</t>
   </si>
 </sst>
 </file>
@@ -694,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BC54"/>
+  <dimension ref="A1:BF54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.140625" bestFit="1" customWidth="1"/>
@@ -711,7 +714,7 @@
     <col min="36" max="36" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:55" s="4" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:58" s="4" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3" t="s">
@@ -873,8 +876,17 @@
       <c r="BC1" s="3" t="s">
         <v>71</v>
       </c>
+      <c r="BD1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="BE1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="BF1" s="3" t="s">
+        <v>71</v>
+      </c>
     </row>
-    <row r="2" spans="1:55" ht="21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="6">
         <v>46265</v>
@@ -1038,8 +1050,17 @@
       <c r="BC2" s="6">
         <v>46318</v>
       </c>
+      <c r="BD2" s="6">
+        <v>46319</v>
+      </c>
+      <c r="BE2" s="6">
+        <v>46320</v>
+      </c>
+      <c r="BF2" s="6">
+        <v>46321</v>
+      </c>
     </row>
-    <row r="3" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>32</v>
       </c>
@@ -1201,8 +1222,15 @@
       <c r="BC3" s="8">
         <v>0</v>
       </c>
+      <c r="BD3" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE3" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF3" s="8"/>
     </row>
-    <row r="4" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>34</v>
       </c>
@@ -1368,8 +1396,17 @@
       <c r="BC4" s="8">
         <v>108</v>
       </c>
+      <c r="BD4" s="8">
+        <v>108</v>
+      </c>
+      <c r="BE4" s="8">
+        <v>130</v>
+      </c>
+      <c r="BF4" s="8">
+        <v>112</v>
+      </c>
     </row>
-    <row r="5" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1535,8 +1572,17 @@
       <c r="BC5" s="8">
         <v>34</v>
       </c>
+      <c r="BD5" s="8">
+        <v>55</v>
+      </c>
+      <c r="BE5" s="8">
+        <v>72</v>
+      </c>
+      <c r="BF5" s="8">
+        <v>59</v>
+      </c>
     </row>
-    <row r="6" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>36</v>
       </c>
@@ -1702,8 +1748,17 @@
       <c r="BC6" s="8">
         <v>36</v>
       </c>
+      <c r="BD6" s="8">
+        <v>58</v>
+      </c>
+      <c r="BE6" s="8">
+        <v>63</v>
+      </c>
+      <c r="BF6" s="8">
+        <v>61</v>
+      </c>
     </row>
-    <row r="7" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>37</v>
       </c>
@@ -1869,8 +1924,17 @@
       <c r="BC7" s="8">
         <v>88</v>
       </c>
+      <c r="BD7" s="8">
+        <v>106</v>
+      </c>
+      <c r="BE7" s="8">
+        <v>134</v>
+      </c>
+      <c r="BF7" s="8">
+        <v>130</v>
+      </c>
     </row>
-    <row r="8" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>38</v>
       </c>
@@ -2036,8 +2100,17 @@
       <c r="BC8" s="8">
         <v>125</v>
       </c>
+      <c r="BD8" s="8">
+        <v>87</v>
+      </c>
+      <c r="BE8" s="8">
+        <v>147</v>
+      </c>
+      <c r="BF8" s="8">
+        <v>135</v>
+      </c>
     </row>
-    <row r="9" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>39</v>
       </c>
@@ -2203,8 +2276,17 @@
       <c r="BC9" s="8">
         <v>99</v>
       </c>
+      <c r="BD9" s="8">
+        <v>86</v>
+      </c>
+      <c r="BE9" s="8">
+        <v>95</v>
+      </c>
+      <c r="BF9" s="8">
+        <v>94</v>
+      </c>
     </row>
-    <row r="10" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>40</v>
       </c>
@@ -2370,8 +2452,17 @@
       <c r="BC10" s="8">
         <v>77</v>
       </c>
+      <c r="BD10" s="8">
+        <v>114</v>
+      </c>
+      <c r="BE10" s="8">
+        <v>120</v>
+      </c>
+      <c r="BF10" s="8">
+        <v>98</v>
+      </c>
     </row>
-    <row r="11" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
@@ -2537,8 +2628,17 @@
       <c r="BC11" s="8">
         <v>33</v>
       </c>
+      <c r="BD11" s="8">
+        <v>42</v>
+      </c>
+      <c r="BE11" s="8">
+        <v>64</v>
+      </c>
+      <c r="BF11" s="8">
+        <v>56</v>
+      </c>
     </row>
-    <row r="12" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -2704,8 +2804,17 @@
       <c r="BC12" s="8">
         <v>38</v>
       </c>
+      <c r="BD12" s="8">
+        <v>53</v>
+      </c>
+      <c r="BE12" s="8">
+        <v>58</v>
+      </c>
+      <c r="BF12" s="8">
+        <v>57</v>
+      </c>
     </row>
-    <row r="13" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2980,17 @@
       <c r="BC13" s="8">
         <v>116</v>
       </c>
+      <c r="BD13" s="8">
+        <v>108</v>
+      </c>
+      <c r="BE13" s="8">
+        <v>122</v>
+      </c>
+      <c r="BF13" s="8">
+        <v>123</v>
+      </c>
     </row>
-    <row r="14" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>44</v>
       </c>
@@ -3038,8 +3156,17 @@
       <c r="BC14" s="8">
         <v>116</v>
       </c>
+      <c r="BD14" s="8">
+        <v>87</v>
+      </c>
+      <c r="BE14" s="8">
+        <v>116</v>
+      </c>
+      <c r="BF14" s="8">
+        <v>114</v>
+      </c>
     </row>
-    <row r="15" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>45</v>
       </c>
@@ -3205,8 +3332,17 @@
       <c r="BC15" s="8">
         <v>125</v>
       </c>
+      <c r="BD15" s="8">
+        <v>93</v>
+      </c>
+      <c r="BE15" s="8">
+        <v>129</v>
+      </c>
+      <c r="BF15" s="8">
+        <v>135</v>
+      </c>
     </row>
-    <row r="16" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -3372,8 +3508,17 @@
       <c r="BC16" s="8">
         <v>69</v>
       </c>
+      <c r="BD16" s="8">
+        <v>64</v>
+      </c>
+      <c r="BE16" s="8">
+        <v>89</v>
+      </c>
+      <c r="BF16" s="8">
+        <v>95</v>
+      </c>
     </row>
-    <row r="17" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>47</v>
       </c>
@@ -3539,8 +3684,17 @@
       <c r="BC17" s="8">
         <v>70</v>
       </c>
+      <c r="BD17" s="8">
+        <v>91</v>
+      </c>
+      <c r="BE17" s="8">
+        <v>82</v>
+      </c>
+      <c r="BF17" s="8">
+        <v>94</v>
+      </c>
     </row>
-    <row r="18" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>48</v>
       </c>
@@ -3706,8 +3860,17 @@
       <c r="BC18" s="8">
         <v>35</v>
       </c>
+      <c r="BD18" s="8">
+        <v>44</v>
+      </c>
+      <c r="BE18" s="8">
+        <v>56</v>
+      </c>
+      <c r="BF18" s="8">
+        <v>47</v>
+      </c>
     </row>
-    <row r="19" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>49</v>
       </c>
@@ -3873,8 +4036,17 @@
       <c r="BC19" s="8">
         <v>33</v>
       </c>
+      <c r="BD19" s="8">
+        <v>42</v>
+      </c>
+      <c r="BE19" s="8">
+        <v>49</v>
+      </c>
+      <c r="BF19" s="8">
+        <v>50</v>
+      </c>
     </row>
-    <row r="20" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>50</v>
       </c>
@@ -4040,8 +4212,17 @@
       <c r="BC20" s="8">
         <v>125</v>
       </c>
+      <c r="BD20" s="8">
+        <v>88</v>
+      </c>
+      <c r="BE20" s="8">
+        <v>94</v>
+      </c>
+      <c r="BF20" s="8">
+        <v>108</v>
+      </c>
     </row>
-    <row r="21" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -4207,8 +4388,17 @@
       <c r="BC21" s="8">
         <v>96</v>
       </c>
+      <c r="BD21" s="8">
+        <v>90</v>
+      </c>
+      <c r="BE21" s="8">
+        <v>102</v>
+      </c>
+      <c r="BF21" s="8">
+        <v>110</v>
+      </c>
     </row>
-    <row r="22" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>52</v>
       </c>
@@ -4374,8 +4564,17 @@
       <c r="BC22" s="8">
         <v>62</v>
       </c>
+      <c r="BD22" s="8">
+        <v>69</v>
+      </c>
+      <c r="BE22" s="8">
+        <v>59</v>
+      </c>
+      <c r="BF22" s="8">
+        <v>73</v>
+      </c>
     </row>
-    <row r="23" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>53</v>
       </c>
@@ -4541,8 +4740,17 @@
       <c r="BC23" s="8">
         <v>72</v>
       </c>
+      <c r="BD23" s="8">
+        <v>98</v>
+      </c>
+      <c r="BE23" s="8">
+        <v>89</v>
+      </c>
+      <c r="BF23" s="8">
+        <v>97</v>
+      </c>
     </row>
-    <row r="24" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>54</v>
       </c>
@@ -4708,8 +4916,17 @@
       <c r="BC24" s="8">
         <v>96</v>
       </c>
+      <c r="BD24" s="8">
+        <v>111</v>
+      </c>
+      <c r="BE24" s="8">
+        <v>131</v>
+      </c>
+      <c r="BF24" s="8">
+        <v>112</v>
+      </c>
     </row>
-    <row r="25" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>55</v>
       </c>
@@ -4875,8 +5092,17 @@
       <c r="BC25" s="8">
         <v>96</v>
       </c>
+      <c r="BD25" s="8">
+        <v>104</v>
+      </c>
+      <c r="BE25" s="8">
+        <v>110</v>
+      </c>
+      <c r="BF25" s="8">
+        <v>114</v>
+      </c>
     </row>
-    <row r="26" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>56</v>
       </c>
@@ -5042,8 +5268,17 @@
       <c r="BC26" s="8">
         <v>69</v>
       </c>
+      <c r="BD26" s="8">
+        <v>88</v>
+      </c>
+      <c r="BE26" s="8">
+        <v>95</v>
+      </c>
+      <c r="BF26" s="8">
+        <v>86</v>
+      </c>
     </row>
-    <row r="27" spans="1:55" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:58" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>57</v>
       </c>
@@ -5136,7 +5371,7 @@
         <v>1484</v>
       </c>
       <c r="X27" s="12">
-        <f t="shared" ref="X27:BC27" si="3">SUM(X3:X26)</f>
+        <f t="shared" ref="X27:BF27" si="3">SUM(X3:X26)</f>
         <v>1474</v>
       </c>
       <c r="Y27" s="12">
@@ -5263,12 +5498,24 @@
         <f t="shared" si="3"/>
         <v>1818</v>
       </c>
+      <c r="BD27" s="10">
+        <f t="shared" si="3"/>
+        <v>1886</v>
+      </c>
+      <c r="BE27" s="10">
+        <f t="shared" si="3"/>
+        <v>2206</v>
+      </c>
+      <c r="BF27" s="10">
+        <f>SUM(BF3:BF26)</f>
+        <v>2160</v>
+      </c>
     </row>
-    <row r="28" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F28" s="13"/>
       <c r="U28" s="14"/>
     </row>
-    <row r="29" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
       <c r="X29" s="15"/>
@@ -5278,7 +5525,7 @@
       <c r="AB29" s="15"/>
       <c r="AC29" s="15"/>
     </row>
-    <row r="30" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F30" s="13"/>
       <c r="G30" s="13"/>
       <c r="V30" s="13"/>
@@ -5291,7 +5538,7 @@
       <c r="AI30" s="13"/>
       <c r="AJ30" s="13"/>
     </row>
-    <row r="31" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F31" s="13"/>
       <c r="G31" s="13"/>
       <c r="V31" s="13"/>
@@ -5304,7 +5551,7 @@
       <c r="AI31" s="13"/>
       <c r="AJ31" s="13"/>
     </row>
-    <row r="32" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F32" s="13"/>
       <c r="G32" s="13"/>
       <c r="V32" s="13"/>

--- a/2026 pasta satış.xlsx
+++ b/2026 pasta satış.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="74">
   <si>
     <t>30°C – Açık</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>20°C –Güneşli</t>
+  </si>
+  <si>
+    <t>13°C - hafif yağmurlu</t>
   </si>
 </sst>
 </file>
@@ -697,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BF54"/>
+  <dimension ref="A1:BG54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.140625" bestFit="1" customWidth="1"/>
@@ -714,7 +717,7 @@
     <col min="36" max="36" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" s="4" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:59" s="4" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3" t="s">
@@ -885,8 +888,11 @@
       <c r="BF1" s="3" t="s">
         <v>71</v>
       </c>
+      <c r="BG1" s="3" t="s">
+        <v>73</v>
+      </c>
     </row>
-    <row r="2" spans="1:58" ht="21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:59" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="6">
         <v>46265</v>
@@ -1059,8 +1065,11 @@
       <c r="BF2" s="6">
         <v>46321</v>
       </c>
+      <c r="BG2" s="6">
+        <v>46322</v>
+      </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>32</v>
       </c>
@@ -1228,9 +1237,14 @@
       <c r="BE3" s="8">
         <v>0</v>
       </c>
-      <c r="BF3" s="8"/>
+      <c r="BF3" s="8">
+        <v>0</v>
+      </c>
+      <c r="BG3" s="8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>34</v>
       </c>
@@ -1405,8 +1419,11 @@
       <c r="BF4" s="8">
         <v>112</v>
       </c>
+      <c r="BG4" s="8">
+        <v>84</v>
+      </c>
     </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1581,8 +1598,11 @@
       <c r="BF5" s="8">
         <v>59</v>
       </c>
+      <c r="BG5" s="8">
+        <v>43</v>
+      </c>
     </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>36</v>
       </c>
@@ -1757,8 +1777,11 @@
       <c r="BF6" s="8">
         <v>61</v>
       </c>
+      <c r="BG6" s="8">
+        <v>36</v>
+      </c>
     </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>37</v>
       </c>
@@ -1933,8 +1956,11 @@
       <c r="BF7" s="8">
         <v>130</v>
       </c>
+      <c r="BG7" s="8">
+        <v>82</v>
+      </c>
     </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>38</v>
       </c>
@@ -2109,8 +2135,11 @@
       <c r="BF8" s="8">
         <v>135</v>
       </c>
+      <c r="BG8" s="8">
+        <v>88</v>
+      </c>
     </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>39</v>
       </c>
@@ -2285,8 +2314,11 @@
       <c r="BF9" s="8">
         <v>94</v>
       </c>
+      <c r="BG9" s="8">
+        <v>69</v>
+      </c>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>40</v>
       </c>
@@ -2461,8 +2493,11 @@
       <c r="BF10" s="8">
         <v>98</v>
       </c>
+      <c r="BG10" s="8">
+        <v>96</v>
+      </c>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
@@ -2637,8 +2672,11 @@
       <c r="BF11" s="8">
         <v>56</v>
       </c>
+      <c r="BG11" s="8">
+        <v>35</v>
+      </c>
     </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -2813,8 +2851,11 @@
       <c r="BF12" s="8">
         <v>57</v>
       </c>
+      <c r="BG12" s="8">
+        <v>47</v>
+      </c>
     </row>
-    <row r="13" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>43</v>
       </c>
@@ -2989,8 +3030,11 @@
       <c r="BF13" s="8">
         <v>123</v>
       </c>
+      <c r="BG13" s="8">
+        <v>85</v>
+      </c>
     </row>
-    <row r="14" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>44</v>
       </c>
@@ -3165,8 +3209,11 @@
       <c r="BF14" s="8">
         <v>114</v>
       </c>
+      <c r="BG14" s="8">
+        <v>75</v>
+      </c>
     </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>45</v>
       </c>
@@ -3341,8 +3388,11 @@
       <c r="BF15" s="8">
         <v>135</v>
       </c>
+      <c r="BG15" s="8">
+        <v>92</v>
+      </c>
     </row>
-    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -3517,8 +3567,11 @@
       <c r="BF16" s="8">
         <v>95</v>
       </c>
+      <c r="BG16" s="8">
+        <v>72</v>
+      </c>
     </row>
-    <row r="17" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>47</v>
       </c>
@@ -3693,8 +3746,11 @@
       <c r="BF17" s="8">
         <v>94</v>
       </c>
+      <c r="BG17" s="8">
+        <v>72</v>
+      </c>
     </row>
-    <row r="18" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>48</v>
       </c>
@@ -3869,8 +3925,11 @@
       <c r="BF18" s="8">
         <v>47</v>
       </c>
+      <c r="BG18" s="8">
+        <v>33</v>
+      </c>
     </row>
-    <row r="19" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>49</v>
       </c>
@@ -4045,8 +4104,11 @@
       <c r="BF19" s="8">
         <v>50</v>
       </c>
+      <c r="BG19" s="8">
+        <v>36</v>
+      </c>
     </row>
-    <row r="20" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>50</v>
       </c>
@@ -4221,8 +4283,11 @@
       <c r="BF20" s="8">
         <v>108</v>
       </c>
+      <c r="BG20" s="8">
+        <v>72</v>
+      </c>
     </row>
-    <row r="21" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -4397,8 +4462,11 @@
       <c r="BF21" s="8">
         <v>110</v>
       </c>
+      <c r="BG21" s="8">
+        <v>89</v>
+      </c>
     </row>
-    <row r="22" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>52</v>
       </c>
@@ -4573,8 +4641,11 @@
       <c r="BF22" s="8">
         <v>73</v>
       </c>
+      <c r="BG22" s="8">
+        <v>60</v>
+      </c>
     </row>
-    <row r="23" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>53</v>
       </c>
@@ -4749,8 +4820,11 @@
       <c r="BF23" s="8">
         <v>97</v>
       </c>
+      <c r="BG23" s="8">
+        <v>56</v>
+      </c>
     </row>
-    <row r="24" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>54</v>
       </c>
@@ -4925,8 +4999,11 @@
       <c r="BF24" s="8">
         <v>112</v>
       </c>
+      <c r="BG24" s="8">
+        <v>84</v>
+      </c>
     </row>
-    <row r="25" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>55</v>
       </c>
@@ -5101,8 +5178,11 @@
       <c r="BF25" s="8">
         <v>114</v>
       </c>
+      <c r="BG25" s="8">
+        <v>91</v>
+      </c>
     </row>
-    <row r="26" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>56</v>
       </c>
@@ -5277,8 +5357,11 @@
       <c r="BF26" s="8">
         <v>86</v>
       </c>
+      <c r="BG26" s="8">
+        <v>85</v>
+      </c>
     </row>
-    <row r="27" spans="1:58" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:59" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>57</v>
       </c>
@@ -5371,7 +5454,7 @@
         <v>1484</v>
       </c>
       <c r="X27" s="12">
-        <f t="shared" ref="X27:BF27" si="3">SUM(X3:X26)</f>
+        <f t="shared" ref="X27:BE27" si="3">SUM(X3:X26)</f>
         <v>1474</v>
       </c>
       <c r="Y27" s="12">
@@ -5510,12 +5593,16 @@
         <f>SUM(BF3:BF26)</f>
         <v>2160</v>
       </c>
+      <c r="BG27" s="10">
+        <f>SUM(BG3:BG26)</f>
+        <v>1582</v>
+      </c>
     </row>
-    <row r="28" spans="1:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F28" s="13"/>
       <c r="U28" s="14"/>
     </row>
-    <row r="29" spans="1:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
       <c r="X29" s="15"/>
@@ -5525,7 +5612,7 @@
       <c r="AB29" s="15"/>
       <c r="AC29" s="15"/>
     </row>
-    <row r="30" spans="1:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F30" s="13"/>
       <c r="G30" s="13"/>
       <c r="V30" s="13"/>
@@ -5538,7 +5625,7 @@
       <c r="AI30" s="13"/>
       <c r="AJ30" s="13"/>
     </row>
-    <row r="31" spans="1:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F31" s="13"/>
       <c r="G31" s="13"/>
       <c r="V31" s="13"/>
@@ -5551,7 +5638,7 @@
       <c r="AI31" s="13"/>
       <c r="AJ31" s="13"/>
     </row>
-    <row r="32" spans="1:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F32" s="13"/>
       <c r="G32" s="13"/>
       <c r="V32" s="13"/>

--- a/2026 pasta satış.xlsx
+++ b/2026 pasta satış.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="75">
   <si>
     <t>30°C – Açık</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>13°C - hafif yağmurlu</t>
+  </si>
+  <si>
+    <t>17°C - bulutlu</t>
   </si>
 </sst>
 </file>
@@ -700,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BG54"/>
+  <dimension ref="A1:BK54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.140625" bestFit="1" customWidth="1"/>
@@ -717,7 +720,7 @@
     <col min="36" max="36" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" s="4" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:63" s="4" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3" t="s">
@@ -891,8 +894,14 @@
       <c r="BG1" s="3" t="s">
         <v>73</v>
       </c>
+      <c r="BH1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI1" s="3"/>
+      <c r="BJ1" s="3"/>
+      <c r="BK1" s="3"/>
     </row>
-    <row r="2" spans="1:59" ht="21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:63" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="6">
         <v>46265</v>
@@ -1068,8 +1077,20 @@
       <c r="BG2" s="6">
         <v>46322</v>
       </c>
+      <c r="BH2" s="6">
+        <v>46323</v>
+      </c>
+      <c r="BI2" s="6">
+        <v>46324</v>
+      </c>
+      <c r="BJ2" s="6">
+        <v>46325</v>
+      </c>
+      <c r="BK2" s="6">
+        <v>46326</v>
+      </c>
     </row>
-    <row r="3" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>32</v>
       </c>
@@ -1243,8 +1264,14 @@
       <c r="BG3" s="8">
         <v>0</v>
       </c>
+      <c r="BH3" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI3" s="8"/>
+      <c r="BJ3" s="8"/>
+      <c r="BK3" s="8"/>
     </row>
-    <row r="4" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>34</v>
       </c>
@@ -1422,8 +1449,14 @@
       <c r="BG4" s="8">
         <v>84</v>
       </c>
+      <c r="BH4" s="8">
+        <v>75</v>
+      </c>
+      <c r="BI4" s="8"/>
+      <c r="BJ4" s="8"/>
+      <c r="BK4" s="8"/>
     </row>
-    <row r="5" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1601,8 +1634,14 @@
       <c r="BG5" s="8">
         <v>43</v>
       </c>
+      <c r="BH5" s="8">
+        <v>44</v>
+      </c>
+      <c r="BI5" s="8"/>
+      <c r="BJ5" s="8"/>
+      <c r="BK5" s="8"/>
     </row>
-    <row r="6" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>36</v>
       </c>
@@ -1780,8 +1819,14 @@
       <c r="BG6" s="8">
         <v>36</v>
       </c>
+      <c r="BH6" s="8">
+        <v>40</v>
+      </c>
+      <c r="BI6" s="8"/>
+      <c r="BJ6" s="8"/>
+      <c r="BK6" s="8"/>
     </row>
-    <row r="7" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>37</v>
       </c>
@@ -1959,8 +2004,14 @@
       <c r="BG7" s="8">
         <v>82</v>
       </c>
+      <c r="BH7" s="8">
+        <v>97</v>
+      </c>
+      <c r="BI7" s="8"/>
+      <c r="BJ7" s="8"/>
+      <c r="BK7" s="8"/>
     </row>
-    <row r="8" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>38</v>
       </c>
@@ -2138,8 +2189,14 @@
       <c r="BG8" s="8">
         <v>88</v>
       </c>
+      <c r="BH8" s="8">
+        <v>85</v>
+      </c>
+      <c r="BI8" s="8"/>
+      <c r="BJ8" s="8"/>
+      <c r="BK8" s="8"/>
     </row>
-    <row r="9" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>39</v>
       </c>
@@ -2317,8 +2374,14 @@
       <c r="BG9" s="8">
         <v>69</v>
       </c>
+      <c r="BH9" s="8">
+        <v>71</v>
+      </c>
+      <c r="BI9" s="8"/>
+      <c r="BJ9" s="8"/>
+      <c r="BK9" s="8"/>
     </row>
-    <row r="10" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>40</v>
       </c>
@@ -2496,8 +2559,14 @@
       <c r="BG10" s="8">
         <v>96</v>
       </c>
+      <c r="BH10" s="8">
+        <v>78</v>
+      </c>
+      <c r="BI10" s="8"/>
+      <c r="BJ10" s="8"/>
+      <c r="BK10" s="8"/>
     </row>
-    <row r="11" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
@@ -2675,8 +2744,14 @@
       <c r="BG11" s="8">
         <v>35</v>
       </c>
+      <c r="BH11" s="8">
+        <v>42</v>
+      </c>
+      <c r="BI11" s="8"/>
+      <c r="BJ11" s="8"/>
+      <c r="BK11" s="8"/>
     </row>
-    <row r="12" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -2854,8 +2929,14 @@
       <c r="BG12" s="8">
         <v>47</v>
       </c>
+      <c r="BH12" s="8">
+        <v>39</v>
+      </c>
+      <c r="BI12" s="8"/>
+      <c r="BJ12" s="8"/>
+      <c r="BK12" s="8"/>
     </row>
-    <row r="13" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>43</v>
       </c>
@@ -3033,8 +3114,14 @@
       <c r="BG13" s="8">
         <v>85</v>
       </c>
+      <c r="BH13" s="8">
+        <v>94</v>
+      </c>
+      <c r="BI13" s="8"/>
+      <c r="BJ13" s="8"/>
+      <c r="BK13" s="8"/>
     </row>
-    <row r="14" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>44</v>
       </c>
@@ -3212,8 +3299,14 @@
       <c r="BG14" s="8">
         <v>75</v>
       </c>
+      <c r="BH14" s="8">
+        <v>76</v>
+      </c>
+      <c r="BI14" s="8"/>
+      <c r="BJ14" s="8"/>
+      <c r="BK14" s="8"/>
     </row>
-    <row r="15" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>45</v>
       </c>
@@ -3391,8 +3484,14 @@
       <c r="BG15" s="8">
         <v>92</v>
       </c>
+      <c r="BH15" s="8">
+        <v>92</v>
+      </c>
+      <c r="BI15" s="8"/>
+      <c r="BJ15" s="8"/>
+      <c r="BK15" s="8"/>
     </row>
-    <row r="16" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -3570,8 +3669,14 @@
       <c r="BG16" s="8">
         <v>72</v>
       </c>
+      <c r="BH16" s="8">
+        <v>66</v>
+      </c>
+      <c r="BI16" s="8"/>
+      <c r="BJ16" s="8"/>
+      <c r="BK16" s="8"/>
     </row>
-    <row r="17" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>47</v>
       </c>
@@ -3749,8 +3854,14 @@
       <c r="BG17" s="8">
         <v>72</v>
       </c>
+      <c r="BH17" s="8">
+        <v>57</v>
+      </c>
+      <c r="BI17" s="8"/>
+      <c r="BJ17" s="8"/>
+      <c r="BK17" s="8"/>
     </row>
-    <row r="18" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>48</v>
       </c>
@@ -3928,8 +4039,14 @@
       <c r="BG18" s="8">
         <v>33</v>
       </c>
+      <c r="BH18" s="8">
+        <v>39</v>
+      </c>
+      <c r="BI18" s="8"/>
+      <c r="BJ18" s="8"/>
+      <c r="BK18" s="8"/>
     </row>
-    <row r="19" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>49</v>
       </c>
@@ -4107,8 +4224,14 @@
       <c r="BG19" s="8">
         <v>36</v>
       </c>
+      <c r="BH19" s="8">
+        <v>35</v>
+      </c>
+      <c r="BI19" s="8"/>
+      <c r="BJ19" s="8"/>
+      <c r="BK19" s="8"/>
     </row>
-    <row r="20" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>50</v>
       </c>
@@ -4286,8 +4409,14 @@
       <c r="BG20" s="8">
         <v>72</v>
       </c>
+      <c r="BH20" s="8">
+        <v>86</v>
+      </c>
+      <c r="BI20" s="8"/>
+      <c r="BJ20" s="8"/>
+      <c r="BK20" s="8"/>
     </row>
-    <row r="21" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -4465,8 +4594,14 @@
       <c r="BG21" s="8">
         <v>89</v>
       </c>
+      <c r="BH21" s="8">
+        <v>82</v>
+      </c>
+      <c r="BI21" s="8"/>
+      <c r="BJ21" s="8"/>
+      <c r="BK21" s="8"/>
     </row>
-    <row r="22" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>52</v>
       </c>
@@ -4644,8 +4779,14 @@
       <c r="BG22" s="8">
         <v>60</v>
       </c>
+      <c r="BH22" s="8">
+        <v>59</v>
+      </c>
+      <c r="BI22" s="8"/>
+      <c r="BJ22" s="8"/>
+      <c r="BK22" s="8"/>
     </row>
-    <row r="23" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>53</v>
       </c>
@@ -4823,8 +4964,14 @@
       <c r="BG23" s="8">
         <v>56</v>
       </c>
+      <c r="BH23" s="8">
+        <v>74</v>
+      </c>
+      <c r="BI23" s="8"/>
+      <c r="BJ23" s="8"/>
+      <c r="BK23" s="8"/>
     </row>
-    <row r="24" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>54</v>
       </c>
@@ -5002,8 +5149,14 @@
       <c r="BG24" s="8">
         <v>84</v>
       </c>
+      <c r="BH24" s="8">
+        <v>82</v>
+      </c>
+      <c r="BI24" s="8"/>
+      <c r="BJ24" s="8"/>
+      <c r="BK24" s="8"/>
     </row>
-    <row r="25" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>55</v>
       </c>
@@ -5181,8 +5334,14 @@
       <c r="BG25" s="8">
         <v>91</v>
       </c>
+      <c r="BH25" s="8">
+        <v>87</v>
+      </c>
+      <c r="BI25" s="8"/>
+      <c r="BJ25" s="8"/>
+      <c r="BK25" s="8"/>
     </row>
-    <row r="26" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>56</v>
       </c>
@@ -5360,8 +5519,14 @@
       <c r="BG26" s="8">
         <v>85</v>
       </c>
+      <c r="BH26" s="8">
+        <v>92</v>
+      </c>
+      <c r="BI26" s="8"/>
+      <c r="BJ26" s="8"/>
+      <c r="BK26" s="8"/>
     </row>
-    <row r="27" spans="1:59" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:63" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>57</v>
       </c>
@@ -5597,12 +5762,28 @@
         <f>SUM(BG3:BG26)</f>
         <v>1582</v>
       </c>
+      <c r="BH27" s="10">
+        <f t="shared" ref="BH27:BK27" si="4">SUM(BH3:BH26)</f>
+        <v>1592</v>
+      </c>
+      <c r="BI27" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="BJ27" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="BK27" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F28" s="13"/>
       <c r="U28" s="14"/>
     </row>
-    <row r="29" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
       <c r="X29" s="15"/>
@@ -5612,7 +5793,7 @@
       <c r="AB29" s="15"/>
       <c r="AC29" s="15"/>
     </row>
-    <row r="30" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F30" s="13"/>
       <c r="G30" s="13"/>
       <c r="V30" s="13"/>
@@ -5625,7 +5806,7 @@
       <c r="AI30" s="13"/>
       <c r="AJ30" s="13"/>
     </row>
-    <row r="31" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F31" s="13"/>
       <c r="G31" s="13"/>
       <c r="V31" s="13"/>
@@ -5638,7 +5819,7 @@
       <c r="AI31" s="13"/>
       <c r="AJ31" s="13"/>
     </row>
-    <row r="32" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F32" s="13"/>
       <c r="G32" s="13"/>
       <c r="V32" s="13"/>

--- a/2026 pasta satış.xlsx
+++ b/2026 pasta satış.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="76">
   <si>
     <t>30°C – Açık</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>17°C - bulutlu</t>
+  </si>
+  <si>
+    <t>1°C - bulutlu</t>
   </si>
 </sst>
 </file>
@@ -897,7 +900,9 @@
       <c r="BH1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="BI1" s="3"/>
+      <c r="BI1" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="BJ1" s="3"/>
       <c r="BK1" s="3"/>
     </row>
@@ -1267,7 +1272,9 @@
       <c r="BH3" s="8">
         <v>0</v>
       </c>
-      <c r="BI3" s="8"/>
+      <c r="BI3" s="8">
+        <v>0</v>
+      </c>
       <c r="BJ3" s="8"/>
       <c r="BK3" s="8"/>
     </row>
@@ -1452,7 +1459,9 @@
       <c r="BH4" s="8">
         <v>75</v>
       </c>
-      <c r="BI4" s="8"/>
+      <c r="BI4" s="8">
+        <v>104</v>
+      </c>
       <c r="BJ4" s="8"/>
       <c r="BK4" s="8"/>
     </row>
@@ -1637,7 +1646,9 @@
       <c r="BH5" s="8">
         <v>44</v>
       </c>
-      <c r="BI5" s="8"/>
+      <c r="BI5" s="8">
+        <v>60</v>
+      </c>
       <c r="BJ5" s="8"/>
       <c r="BK5" s="8"/>
     </row>
@@ -1822,7 +1833,9 @@
       <c r="BH6" s="8">
         <v>40</v>
       </c>
-      <c r="BI6" s="8"/>
+      <c r="BI6" s="8">
+        <v>56</v>
+      </c>
       <c r="BJ6" s="8"/>
       <c r="BK6" s="8"/>
     </row>
@@ -2007,7 +2020,9 @@
       <c r="BH7" s="8">
         <v>97</v>
       </c>
-      <c r="BI7" s="8"/>
+      <c r="BI7" s="8">
+        <v>113</v>
+      </c>
       <c r="BJ7" s="8"/>
       <c r="BK7" s="8"/>
     </row>
@@ -2192,7 +2207,9 @@
       <c r="BH8" s="8">
         <v>85</v>
       </c>
-      <c r="BI8" s="8"/>
+      <c r="BI8" s="8">
+        <v>129</v>
+      </c>
       <c r="BJ8" s="8"/>
       <c r="BK8" s="8"/>
     </row>
@@ -2377,7 +2394,9 @@
       <c r="BH9" s="8">
         <v>71</v>
       </c>
-      <c r="BI9" s="8"/>
+      <c r="BI9" s="8">
+        <v>100</v>
+      </c>
       <c r="BJ9" s="8"/>
       <c r="BK9" s="8"/>
     </row>
@@ -2562,7 +2581,9 @@
       <c r="BH10" s="8">
         <v>78</v>
       </c>
-      <c r="BI10" s="8"/>
+      <c r="BI10" s="8">
+        <v>110</v>
+      </c>
       <c r="BJ10" s="8"/>
       <c r="BK10" s="8"/>
     </row>
@@ -2747,7 +2768,9 @@
       <c r="BH11" s="8">
         <v>42</v>
       </c>
-      <c r="BI11" s="8"/>
+      <c r="BI11" s="8">
+        <v>59</v>
+      </c>
       <c r="BJ11" s="8"/>
       <c r="BK11" s="8"/>
     </row>
@@ -2932,7 +2955,9 @@
       <c r="BH12" s="8">
         <v>39</v>
       </c>
-      <c r="BI12" s="8"/>
+      <c r="BI12" s="8">
+        <v>54</v>
+      </c>
       <c r="BJ12" s="8"/>
       <c r="BK12" s="8"/>
     </row>
@@ -3117,7 +3142,9 @@
       <c r="BH13" s="8">
         <v>94</v>
       </c>
-      <c r="BI13" s="8"/>
+      <c r="BI13" s="8">
+        <v>109</v>
+      </c>
       <c r="BJ13" s="8"/>
       <c r="BK13" s="8"/>
     </row>
@@ -3302,7 +3329,9 @@
       <c r="BH14" s="8">
         <v>76</v>
       </c>
-      <c r="BI14" s="8"/>
+      <c r="BI14" s="8">
+        <v>102</v>
+      </c>
       <c r="BJ14" s="8"/>
       <c r="BK14" s="8"/>
     </row>
@@ -3487,7 +3516,9 @@
       <c r="BH15" s="8">
         <v>92</v>
       </c>
-      <c r="BI15" s="8"/>
+      <c r="BI15" s="8">
+        <v>112</v>
+      </c>
       <c r="BJ15" s="8"/>
       <c r="BK15" s="8"/>
     </row>
@@ -3672,7 +3703,9 @@
       <c r="BH16" s="8">
         <v>66</v>
       </c>
-      <c r="BI16" s="8"/>
+      <c r="BI16" s="8">
+        <v>86</v>
+      </c>
       <c r="BJ16" s="8"/>
       <c r="BK16" s="8"/>
     </row>
@@ -3857,7 +3890,9 @@
       <c r="BH17" s="8">
         <v>57</v>
       </c>
-      <c r="BI17" s="8"/>
+      <c r="BI17" s="8">
+        <v>76</v>
+      </c>
       <c r="BJ17" s="8"/>
       <c r="BK17" s="8"/>
     </row>
@@ -4042,7 +4077,9 @@
       <c r="BH18" s="8">
         <v>39</v>
       </c>
-      <c r="BI18" s="8"/>
+      <c r="BI18" s="8">
+        <v>41</v>
+      </c>
       <c r="BJ18" s="8"/>
       <c r="BK18" s="8"/>
     </row>
@@ -4227,7 +4264,9 @@
       <c r="BH19" s="8">
         <v>35</v>
       </c>
-      <c r="BI19" s="8"/>
+      <c r="BI19" s="8">
+        <v>37</v>
+      </c>
       <c r="BJ19" s="8"/>
       <c r="BK19" s="8"/>
     </row>
@@ -4412,7 +4451,9 @@
       <c r="BH20" s="8">
         <v>86</v>
       </c>
-      <c r="BI20" s="8"/>
+      <c r="BI20" s="8">
+        <v>93</v>
+      </c>
       <c r="BJ20" s="8"/>
       <c r="BK20" s="8"/>
     </row>
@@ -4597,7 +4638,9 @@
       <c r="BH21" s="8">
         <v>82</v>
       </c>
-      <c r="BI21" s="8"/>
+      <c r="BI21" s="8">
+        <v>106</v>
+      </c>
       <c r="BJ21" s="8"/>
       <c r="BK21" s="8"/>
     </row>
@@ -4782,7 +4825,9 @@
       <c r="BH22" s="8">
         <v>59</v>
       </c>
-      <c r="BI22" s="8"/>
+      <c r="BI22" s="8">
+        <v>70</v>
+      </c>
       <c r="BJ22" s="8"/>
       <c r="BK22" s="8"/>
     </row>
@@ -4967,7 +5012,9 @@
       <c r="BH23" s="8">
         <v>74</v>
       </c>
-      <c r="BI23" s="8"/>
+      <c r="BI23" s="8">
+        <v>85</v>
+      </c>
       <c r="BJ23" s="8"/>
       <c r="BK23" s="8"/>
     </row>
@@ -5152,7 +5199,9 @@
       <c r="BH24" s="8">
         <v>82</v>
       </c>
-      <c r="BI24" s="8"/>
+      <c r="BI24" s="8">
+        <v>119</v>
+      </c>
       <c r="BJ24" s="8"/>
       <c r="BK24" s="8"/>
     </row>
@@ -5337,7 +5386,9 @@
       <c r="BH25" s="8">
         <v>87</v>
       </c>
-      <c r="BI25" s="8"/>
+      <c r="BI25" s="8">
+        <v>105</v>
+      </c>
       <c r="BJ25" s="8"/>
       <c r="BK25" s="8"/>
     </row>
@@ -5522,7 +5573,9 @@
       <c r="BH26" s="8">
         <v>92</v>
       </c>
-      <c r="BI26" s="8"/>
+      <c r="BI26" s="8">
+        <v>90</v>
+      </c>
       <c r="BJ26" s="8"/>
       <c r="BK26" s="8"/>
     </row>
@@ -5768,7 +5821,7 @@
       </c>
       <c r="BI27" s="10">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="BJ27" s="10">
         <f t="shared" si="4"/>
